--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WU\Desktop\台股每日自動分析(chening0704)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4AC5075-5353-4236-BC23-2FED3BC8F01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21A6087A-E877-4FD9-840C-5569DF13A60A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="庫存輸入" sheetId="1" r:id="rId1"/>
@@ -27,24 +27,28 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="67">
-  <si>
-    <t>📊  台股智能分析系統｜庫存輸入表</t>
-  </si>
-  <si>
-    <t>📝  只需填入藍色三欄：A=股票代號  B=持倉成本(元)  C=持有張數（整張填整數，零股填小數，例：300股=0.3）</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="86">
+  <si>
+    <t>📊  台股智能分析系統｜庫存輸入表  v3</t>
+  </si>
+  <si>
+    <t>📝  只需填入藍色三欄：A=股票代號（純數字）  B=持倉成本（元，例：850）  C=持有數量（整張填整數；零股填股數，例：300股直接填300）</t>
   </si>
   <si>
     <t>股票代號
-★ 您填入</t>
+★ 4~5碼數字</t>
   </si>
   <si>
     <t>持倉成本
-★ 元／股（均成本）</t>
-  </si>
-  <si>
-    <t>持有張數
-★ 整張或小數（零股）</t>
+★ 元/股（均成本）</t>
+  </si>
+  <si>
+    <t>數量
+★ 整張(張) 或 零股(股數)</t>
+  </si>
+  <si>
+    <t>單位
+★ 張 或 股</t>
   </si>
   <si>
     <t>股票名稱
@@ -59,10 +63,6 @@
 系統每日計算</t>
   </si>
   <si>
-    <t>持倉市值
-系統每日計算</t>
-  </si>
-  <si>
     <t>綜合評分
 系統分析結果</t>
   </si>
@@ -75,7 +75,7 @@
 系統每日輸出</t>
   </si>
   <si>
-    <t>填寫範例 ── 整張與零股的輸入方式</t>
+    <t>填寫範例 ── 請參考此格式填入「庫存輸入」工作表</t>
   </si>
   <si>
     <t>股票代號★</t>
@@ -84,7 +84,10 @@
     <t>持倉成本★</t>
   </si>
   <si>
-    <t>持有張數★（整張或零股）</t>
+    <t>數量★</t>
+  </si>
+  <si>
+    <t>單位★</t>
   </si>
   <si>
     <t>股票名稱</t>
@@ -96,9 +99,6 @@
     <t>損益%</t>
   </si>
   <si>
-    <t>持倉市值</t>
-  </si>
-  <si>
     <t>綜合評分</t>
   </si>
   <si>
@@ -111,7 +111,16 @@
     <t>2330</t>
   </si>
   <si>
-    <t>台積電（整張：5張（5,000股））</t>
+    <t>850</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>張</t>
+  </si>
+  <si>
+    <t>台積電（整張：5張（=5,000股））</t>
   </si>
   <si>
     <t>系統填入</t>
@@ -132,62 +141,108 @@
     <t>2454</t>
   </si>
   <si>
-    <t>聯發科（整張+零股：2張半（2,500股））</t>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>聯發科（整張：2張（=2,000股））</t>
   </si>
   <si>
     <t>2308</t>
   </si>
   <si>
-    <t>台達電（純零股：300股）</t>
+    <t>320</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>台達電（整張：10張（=10,000股））</t>
   </si>
   <si>
     <t>6488</t>
   </si>
   <si>
-    <t>環球晶（純零股：100股）</t>
+    <t>580</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>股</t>
+  </si>
+  <si>
+    <t>環球晶（零股：直接填300（股數））</t>
   </si>
   <si>
     <t>3711</t>
   </si>
   <si>
-    <t>日月光投（純零股：50股）</t>
+    <t>90</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>日月光投（零股：直接填500（股數））</t>
+  </si>
+  <si>
+    <t>0050</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>元大台灣50（整張：1張）</t>
+  </si>
+  <si>
+    <t>920</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>台積電（零股：直接填150（股數））</t>
   </si>
   <si>
     <t>操作說明</t>
   </si>
   <si>
-    <t>您只需要填三欄</t>
-  </si>
-  <si>
-    <t>A欄：股票代號（4~5碼數字，例：2330）
-B欄：持倉均成本（元，例：850.00）
-C欄：持有張數
-  • 整張：填整數，例 5（表示 5,000股）
-  • 零股：填小數，例 0.3（表示 300股）
-  • 混合：填小數，例 2.5（表示 2,500股）
-計算公式：持有股數 ÷ 1000 = C欄數字</t>
-  </si>
-  <si>
-    <t>零股換算對照表</t>
-  </si>
-  <si>
-    <t>50股  → 0.05
-100股 → 0.1
-200股 → 0.2
-300股 → 0.3
-500股 → 0.5
-1張整 → 1
-1張半（1,500股）→ 1.5
-2張又300股 → 2.3</t>
+    <t>您只需要填四欄</t>
+  </si>
+  <si>
+    <t>A欄：股票代號（4~5碼純數字，例：2330、0050）
+B欄：持倉均成本（元，例：850 表示每股850元）
+C欄：數量
+  • 整張：填張數，例 5（代表5張=5,000股）
+  • 零股：填股數，例 300（代表300股）
+D欄：單位（點選下拉選單）
+  • 選「張」→ C欄填張數
+  • 選「股」→ C欄填股數</t>
+  </si>
+  <si>
+    <t>零股與整張對照</t>
+  </si>
+  <si>
+    <t>整張 1張  = 1,000股 → C填 1，D選「張」
+整張 5張  = 5,000股 → C填 5，D選「張」
+零股 100股         → C填 100，D選「股」
+零股 300股         → C填 300，D選「股」
+零股 500股         → C填 500，D選「股」
+混合（1張+300股）請分兩列輸入同一支股票</t>
   </si>
   <si>
     <t>系統自動處理</t>
   </si>
   <si>
-    <t>D欄：股票名稱（自動從 TWSE 查詢）
-E欄：現價（每日收盤後更新）
-F欄：損益%（自動計算）
-G欄：持倉市值（自動計算）
+    <t>E欄：股票名稱（自動從 TWSE 查詢）
+F欄：現價（每日收盤後更新）
+G欄：損益%（自動計算）
 H欄：綜合評分（0~100分）
 I欄：RF漲機率（AI預測）
 J欄：操作建議（加碼/持有/減碼/停損）</t>
@@ -196,100 +251,98 @@
     <t>注意事項</t>
   </si>
   <si>
-    <t>★ D~J欄請勿手動修改，系統每晚自動更新
-★ 股票代號如有前綴零請完整填入（例：0050）
+    <t>★ E~J欄請勿手動修改，系統每晚自動更新
+★ 股票代號請完整填入（0050不能填50）
 ★ 成本填「均成本」（多次買入後計算加權均價）
-★ 每晚 23:30 系統自動分析並回寫結果</t>
+★ 每晚 23:30 系統自動分析並回寫結果
+★ 修改後重新上傳到 GitHub 倉庫覆蓋即可</t>
+  </si>
+  <si>
+    <t>00905</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>00922</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>2308</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>2330</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>2363</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>2406</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>2516</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>2609</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>2610</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>2881</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>2886</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>5534</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>6443</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>8422</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>5548</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>6407</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>6618</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>0050</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>00905</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>00922</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2027</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2308</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2330</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2363</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2406</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2516</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2609</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2610</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2881</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2886</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>5534</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>6443</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>8422</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>5548</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>6407</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>6618</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.####"/>
-  </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -302,85 +355,85 @@
       <sz val="15"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFDDDDDD"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000080"/>
       <name val="Arial"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF7D6608"/>
+      <name val="Arial"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF777777"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF999999"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF444444"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF2E86C1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000080"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -392,7 +445,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -422,6 +475,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEBF5FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -502,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -516,73 +574,76 @@
     <xf numFmtId="4" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -592,10 +653,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -905,43 +972,42 @@
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
     </row>
     <row r="2" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-    </row>
-    <row r="3" spans="1:10" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+    </row>
+    <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -951,7 +1017,7 @@
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -974,721 +1040,830 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="4">
-        <v>72.8</v>
+      <c r="A4" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="35">
+        <v>13.59</v>
       </c>
       <c r="C4" s="5">
-        <v>3.29</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="7"/>
       <c r="F4" s="7"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="4">
-        <v>13.59</v>
+      <c r="A5" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="35">
+        <v>21.77</v>
       </c>
       <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="35">
+        <v>40.85</v>
+      </c>
+      <c r="C6" s="5">
         <v>2</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="4">
-        <v>21.77</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="D6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+    </row>
+    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="35">
+        <v>1330</v>
+      </c>
+      <c r="C7" s="5">
+        <v>36</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="35">
+        <v>1455</v>
+      </c>
+      <c r="C8" s="5">
+        <v>50</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="35">
+        <v>62.9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>3</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="35">
+        <v>36.65</v>
+      </c>
+      <c r="C10" s="5">
         <v>1</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="4">
-        <v>40.85</v>
-      </c>
-      <c r="C7" s="5">
-        <v>2</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="4">
-        <v>1330</v>
-      </c>
-      <c r="C8" s="5">
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="4">
-        <v>1455</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="4">
-        <v>62.9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>5</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+      <c r="D10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="4">
-        <v>36.65</v>
+      <c r="A11" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="35">
+        <v>22.9</v>
       </c>
       <c r="C11" s="5">
         <v>1</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+      <c r="D11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="9"/>
       <c r="F11" s="9"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
     </row>
     <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="4">
-        <v>22.9</v>
+      <c r="A12" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="35">
+        <v>63</v>
       </c>
       <c r="C12" s="5">
+        <v>460</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="35">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1315</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="35">
+        <v>84.5</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1035</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="35">
+        <v>0.59</v>
+      </c>
+      <c r="C15" s="5">
+        <v>20</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="35">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="C16" s="5">
         <v>1</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="4">
-        <v>63</v>
-      </c>
-      <c r="C13" s="5">
-        <v>0.46</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-    </row>
-    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="4">
-        <v>0</v>
-      </c>
-      <c r="C14" s="5">
-        <v>1.3149999999999999</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="4">
-        <v>84.5</v>
-      </c>
-      <c r="C15" s="5">
-        <v>1.0349999999999999</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-    </row>
-    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="4">
-        <v>0.59</v>
-      </c>
-      <c r="C16" s="5">
-        <v>20</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
+      <c r="D16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="7"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
     </row>
     <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" s="4">
-        <v>39.799999999999997</v>
+      <c r="A17" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="35">
+        <v>52.8</v>
       </c>
       <c r="C17" s="5">
+        <v>1693</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="35">
+        <v>42.7</v>
+      </c>
+      <c r="C18" s="5">
         <v>1</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-    </row>
-    <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="4">
-        <v>52.8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1.6930000000000001</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
+      <c r="D18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="7"/>
       <c r="F18" s="7"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
     </row>
     <row r="19" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" s="4">
-        <v>42.7</v>
+      <c r="A19" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="35">
+        <v>29.5</v>
       </c>
       <c r="C19" s="5">
+        <v>3</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="35">
+        <v>26.5</v>
+      </c>
+      <c r="C20" s="5">
+        <v>319</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="35">
+        <v>30.9</v>
+      </c>
+      <c r="C21" s="5">
         <v>1</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-    </row>
-    <row r="20" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B20" s="4">
-        <v>29.5</v>
-      </c>
-      <c r="C20" s="5">
-        <v>3</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B21" s="4">
+      <c r="D21" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+    </row>
+    <row r="22" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="35">
         <v>26.5</v>
-      </c>
-      <c r="C21" s="5">
-        <v>0.31900000000000001</v>
-      </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-    </row>
-    <row r="22" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="4">
-        <v>30.9</v>
       </c>
       <c r="C22" s="5">
         <v>1</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
+      <c r="D22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="7"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
     </row>
     <row r="23" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>66</v>
+      <c r="A23" s="34" t="s">
+        <v>85</v>
       </c>
       <c r="B23" s="4">
-        <v>26.5</v>
+        <v>73.05</v>
       </c>
       <c r="C23" s="5">
-        <v>1</v>
-      </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
+        <v>3317</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="9"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
     </row>
     <row r="24" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="4"/>
       <c r="C24" s="5"/>
       <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
+      <c r="E24" s="7"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
     </row>
     <row r="25" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="9"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
     </row>
     <row r="26" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="4"/>
       <c r="C26" s="5"/>
       <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
+      <c r="E26" s="7"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
     </row>
     <row r="27" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="9"/>
       <c r="F27" s="9"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
     </row>
     <row r="28" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
       <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
+      <c r="E28" s="7"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
     </row>
     <row r="29" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="9"/>
       <c r="F29" s="9"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
     </row>
     <row r="30" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
       <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
+      <c r="E30" s="7"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
     </row>
     <row r="31" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="9"/>
       <c r="F31" s="9"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
     </row>
     <row r="32" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
       <c r="C32" s="5"/>
       <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
+      <c r="E32" s="7"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
     </row>
     <row r="33" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="9"/>
       <c r="F33" s="9"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="D4:D33" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"張,股"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-    </row>
-    <row r="2" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+    </row>
+    <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="11">
-        <v>850</v>
-      </c>
-      <c r="C3" s="11">
-        <v>5</v>
+      <c r="B3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="E4" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="13" t="s">
+      <c r="E5" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="G5" s="20" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="H5" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="14">
-        <v>1100</v>
-      </c>
-      <c r="C4" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="D4" s="15" t="s">
+      <c r="I5" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="16" t="s">
+      <c r="J5" s="20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="16" t="s">
+      <c r="E8" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="G8" s="14" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
+      <c r="H8" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="17">
-        <v>320</v>
-      </c>
-      <c r="C5" s="17">
-        <v>0.3</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="19" t="s">
+    </row>
+    <row r="9" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="G9" s="17" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="20">
-        <v>580</v>
-      </c>
-      <c r="C6" s="20">
-        <v>0.1</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="23">
-        <v>90</v>
-      </c>
-      <c r="C7" s="23">
-        <v>0.05</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" s="25" t="s">
-        <v>29</v>
+      <c r="H9" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1699,52 +1874,52 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="2" max="2" width="58" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="29"/>
+      <c r="A1" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="30"/>
     </row>
     <row r="2" spans="1:2" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>40</v>
+      <c r="A2" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>42</v>
+      <c r="A3" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>44</v>
+      <c r="A4" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>46</v>
+      <c r="A5" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.64</v>
+        <v>28.12</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0338</v>
+        <v>1.0692</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.1</v>
+        <v>40.91</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8420000000000001</v>
+        <v>0.8792</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>43.65</v>
+        <v>43.85</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.06849999999999999</v>
+        <v>0.07339999999999999</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>2360</v>
+        <v>2455</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.7744</v>
+        <v>0.8459</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>28.7</v>
+        <v>26.7</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2380</v>
+        <v>2425</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6357</v>
+        <v>0.6667000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>28.9</v>
+        <v>26.6</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>66.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G9" s="38" t="n">
-        <v>0.062</v>
+        <v>0.0397</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="G10" s="43" t="n">
-        <v>-0.0232</v>
+        <v>38</v>
+      </c>
+      <c r="G10" s="38" t="n">
+        <v>0.0368</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>12.45</v>
+        <v>12.3</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.4563</v>
+        <v>-0.4629</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1492</v>
+        <v>-0.1476</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>19.5</v>
+        <v>19.95</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>194</v>
+        <v>198.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>113.5</v>
+        <v>113</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.3432</v>
+        <v>0.3373</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>41.7</v>
+        <v>41.65</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>69.678</v>
+        <v>69.5932</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>40.45</v>
-      </c>
-      <c r="G16" s="38" t="n">
-        <v>0.0163</v>
+        <v>39.7</v>
+      </c>
+      <c r="G16" s="43" t="n">
+        <v>-0.0025</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>73.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3958</v>
+        <v>0.3939</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>27.35</v>
+        <v>28.1</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0475</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>105.7</v>
+        <v>107.6</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.447</v>
+        <v>0.473</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1784,6 +1784,8 @@
       <c r="I33" s="9" t="n"/>
       <c r="J33" s="9" t="n"/>
     </row>
+    <row r="34"/>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="44" t="inlineStr">
         <is>
@@ -1792,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-03 07:51</t>
+          <t>2026-06-04 07:14</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -925,7 +925,7 @@
         <v>1.0692</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>0.8792</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>0.07339999999999999</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>0.8459</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>26.7</v>
+        <v>25.9</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>0.6667000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>26.6</v>
+        <v>26.2</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>0.0397</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>0.0368</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>-0.4629</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>-0.1476</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>198.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>0.3373</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>69.5932</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>-0.0025</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>0.3939</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>-0.0475</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>0.473</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-04 07:14</t>
+          <t>2026-06-05 05:19</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>28.12</v>
+        <v>27.75</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0692</v>
+        <v>1.0419</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>25.6</v>
+        <v>17.9</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.91</v>
+        <v>40.39</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8792</v>
+        <v>0.8553000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>25.6</v>
+        <v>17.9</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>43.85</v>
+        <v>44.1</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.07339999999999999</v>
+        <v>0.0796</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>25.6</v>
+        <v>17.9</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>2455</v>
+        <v>2425</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.8459</v>
+        <v>0.8233</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>25.9</v>
+        <v>16.1</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2425</v>
+        <v>2385</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.6392</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>26.2</v>
+        <v>18.1</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>65.40000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="G9" s="38" t="n">
-        <v>0.0397</v>
+        <v>0.0032</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>25.6</v>
+        <v>15.7</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>0.0368</v>
+        <v>0.0505</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>25.6</v>
+        <v>20</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>-0.4629</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>25.6</v>
+        <v>15.7</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>53.7</v>
+        <v>53.2</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1476</v>
+        <v>-0.1556</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>25.6</v>
+        <v>15.7</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>19.95</v>
+        <v>19.9</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>198.5</v>
+        <v>198</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>25.6</v>
+        <v>17.9</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.3373</v>
+        <v>0.3491</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>25.6</v>
+        <v>17.9</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>41.65</v>
+        <v>42.1</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>69.5932</v>
+        <v>70.35590000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>25.6</v>
+        <v>17.9</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>39.7</v>
+        <v>39.15</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0025</v>
+        <v>-0.0163</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>25.6</v>
+        <v>15.7</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>73.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3939</v>
+        <v>0.4053</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>25.6</v>
+        <v>16.2</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>28.1</v>
+        <v>28.25</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0475</v>
+        <v>-0.0424</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>25.6</v>
+        <v>17.9</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>107.6</v>
+        <v>106.1</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.473</v>
+        <v>0.4524</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>25.6</v>
+        <v>17.9</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-05 05:19</t>
+          <t>2026-06-05 12:04</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -925,7 +925,7 @@
         <v>1.0419</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>0.8553000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>0.0796</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>17.9</v>
+        <v>24.5</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>0.8233</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>16.1</v>
+        <v>15.3</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>0.6392</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>0.0032</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>15.7</v>
+        <v>16.4</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>0.0505</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>20</v>
+        <v>25.6</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>-0.4629</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>15.7</v>
+        <v>23.9</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>-0.1556</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>15.7</v>
+        <v>24.9</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>198</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>17.9</v>
+        <v>26</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>0.3491</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>17.9</v>
+        <v>23</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>70.35590000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>17.9</v>
+        <v>23</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>-0.0163</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>15.7</v>
+        <v>16.4</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>0.4053</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>16.2</v>
+        <v>25.4</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>-0.0424</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>17.9</v>
+        <v>18.6</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>0.4524</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>17.9</v>
+        <v>21.3</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-05 12:04</t>
+          <t>2026-06-05 14:53</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.75</v>
+        <v>27.18</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0419</v>
+        <v>1</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>17.1</v>
+        <v>11.8</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.39</v>
+        <v>39.69</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8553000000000001</v>
+        <v>0.8231999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>17.1</v>
+        <v>12.6</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>44.1</v>
+        <v>43.8</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.0796</v>
+        <v>0.0722</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>24.5</v>
+        <v>20.9</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>2425</v>
+        <v>2300</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.8233</v>
+        <v>0.7293000000000001</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>15.3</v>
+        <v>11.6</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2385</v>
+        <v>2365</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6392</v>
+        <v>0.6254</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>17.7</v>
+        <v>11.5</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>63.1</v>
-      </c>
-      <c r="G9" s="38" t="n">
-        <v>0.0032</v>
+        <v>62.5</v>
+      </c>
+      <c r="G9" s="43" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>16.4</v>
+        <v>12.8</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="G10" s="38" t="n">
-        <v>0.0505</v>
+        <v>34.65</v>
+      </c>
+      <c r="G10" s="43" t="n">
+        <v>-0.0546</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>25.6</v>
+        <v>11.3</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>12.3</v>
+        <v>12.65</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.4629</v>
+        <v>-0.4476</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>23.9</v>
+        <v>22.4</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>53.2</v>
+        <v>54.5</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1556</v>
+        <v>-0.1349</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>24.9</v>
+        <v>29.4</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>19.9</v>
+        <v>19.95</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>198</v>
+        <v>198.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>26</v>
+        <v>22.4</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.3491</v>
+        <v>0.3964</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>23</v>
+        <v>19.4</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>42.1</v>
+        <v>41.95</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>70.35590000000001</v>
+        <v>70.10169999999999</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>23</v>
+        <v>19.4</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>39.15</v>
+        <v>38.4</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0163</v>
+        <v>-0.0352</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>16.4</v>
+        <v>14.1</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>74.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4053</v>
+        <v>0.4659</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>25.4</v>
+        <v>32.6</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>28.25</v>
+        <v>28.1</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0424</v>
+        <v>-0.0475</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>18.6</v>
+        <v>14.9</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>106.1</v>
+        <v>104.15</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4524</v>
+        <v>0.4257</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>21.3</v>
+        <v>15.6</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-05 14:53</t>
+          <t>2026-06-08 07:51</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-08 07:51</t>
+          <t>2026-06-08 08:38</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.18</v>
+        <v>26.23</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1</v>
+        <v>0.9301</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>11.8</v>
+        <v>18.1</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>39.69</v>
+        <v>38.47</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8231999999999999</v>
+        <v>0.7670999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>12.6</v>
+        <v>18.1</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>43.8</v>
+        <v>41.8</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.0722</v>
+        <v>0.0233</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>20.9</v>
+        <v>26.4</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>2300</v>
+        <v>2255</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.7293000000000001</v>
+        <v>0.6955</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>11.6</v>
+        <v>19.3</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2365</v>
+        <v>2295</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6254</v>
+        <v>0.5772999999999999</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>11.5</v>
+        <v>19.6</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>62.5</v>
+        <v>57.1</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.0064</v>
+        <v>-0.0922</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>12.8</v>
+        <v>20.7</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>34.65</v>
+        <v>32</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.0546</v>
+        <v>-0.1269</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>11.3</v>
+        <v>17.7</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>12.65</v>
+        <v>12.95</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.4476</v>
+        <v>-0.4345000000000001</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>22.4</v>
+        <v>37.7</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>54.5</v>
+        <v>51.7</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1349</v>
+        <v>-0.1794</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>29.4</v>
+        <v>25.6</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>19.95</v>
+        <v>19.05</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>198.5</v>
+        <v>189.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>22.4</v>
+        <v>26.6</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.3964</v>
+        <v>0.3728</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>19.4</v>
+        <v>27.1</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>41.95</v>
+        <v>41.2</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>70.10169999999999</v>
+        <v>68.8305</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>19.4</v>
+        <v>23.6</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>38.4</v>
+        <v>37.5</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0352</v>
+        <v>-0.0578</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>14.1</v>
+        <v>19.2</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>77.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4659</v>
+        <v>0.4545</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>32.6</v>
+        <v>28.5</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>28.1</v>
+        <v>26.95</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0475</v>
+        <v>-0.0864</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>14.9</v>
+        <v>21.6</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>104.15</v>
+        <v>100.95</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4257</v>
+        <v>0.3819</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>15.6</v>
+        <v>21.9</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-08 08:38</t>
+          <t>2026-06-09 05:30</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.23</v>
+        <v>27.28</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9301</v>
+        <v>1.0074</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>18.1</v>
+        <v>16.2</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>38.47</v>
+        <v>39.65</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.7670999999999999</v>
+        <v>0.8212999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>18.1</v>
+        <v>16.2</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>41.8</v>
+        <v>42.9</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.0233</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>26.4</v>
+        <v>23.6</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>2255</v>
+        <v>2415</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.6955</v>
+        <v>0.8158</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>19.3</v>
+        <v>19.9</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2295</v>
+        <v>2305</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.5772999999999999</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>19.6</v>
+        <v>16.8</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>57.1</v>
+        <v>58.3</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.0922</v>
+        <v>-0.0731</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>20.7</v>
+        <v>19.1</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1269</v>
+        <v>-0.045</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>17.7</v>
+        <v>16.2</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>12.95</v>
+        <v>13</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.4345000000000001</v>
+        <v>-0.4323</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>37.7</v>
+        <v>27.2</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1794</v>
+        <v>-0.181</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>25.6</v>
+        <v>24.9</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>19.05</v>
+        <v>19.5</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>189.5</v>
+        <v>194</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.3728</v>
+        <v>0.4793</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>27.1</v>
+        <v>24.2</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>41.2</v>
+        <v>43.55</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>68.8305</v>
+        <v>72.81359999999999</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>23.6</v>
+        <v>30</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.5</v>
+        <v>37.35</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0578</v>
+        <v>-0.0616</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>19.2</v>
+        <v>17.7</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>76.8</v>
+        <v>77.7</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4545</v>
+        <v>0.4716</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>28.5</v>
+        <v>25.7</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.95</v>
-      </c>
-      <c r="G19" s="43" t="n">
-        <v>-0.0864</v>
+        <v>29.6</v>
+      </c>
+      <c r="G19" s="38" t="n">
+        <v>0.0034</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>21.6</v>
+        <v>25.1</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>100.95</v>
+        <v>103.5</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.3819</v>
+        <v>0.4168</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>21.9</v>
+        <v>16.2</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-09 05:30</t>
+          <t>2026-06-10 05:26</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.28</v>
+        <v>26.33</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0074</v>
+        <v>0.9375</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>16.2</v>
+        <v>11.8</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>39.65</v>
+        <v>38.34</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8212999999999999</v>
+        <v>0.7611</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>16.2</v>
+        <v>12.6</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>42.9</v>
+        <v>42.5</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.05019999999999999</v>
+        <v>0.0404</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>23.6</v>
+        <v>18.8</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>2415</v>
+        <v>2200</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.8158</v>
+        <v>0.6541</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>19.9</v>
+        <v>12</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2305</v>
+        <v>2255</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.5498</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>16.8</v>
+        <v>12.8</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>58.3</v>
+        <v>55.1</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.0731</v>
+        <v>-0.124</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>19.1</v>
+        <v>14.3</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>35</v>
+        <v>35.85</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.045</v>
+        <v>-0.0218</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>16.2</v>
+        <v>14.7</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.4323</v>
+        <v>-0.4279</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>27.2</v>
+        <v>23.4</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>51.6</v>
+        <v>50.6</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.181</v>
+        <v>-0.1968</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>24.9</v>
+        <v>18.8</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>19.5</v>
+        <v>19.55</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>194</v>
+        <v>194.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>26.4</v>
+        <v>20.2</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>125</v>
+        <v>122.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.4793</v>
+        <v>0.4497</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>24.2</v>
+        <v>17.3</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>43.55</v>
+        <v>43.4</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>72.81359999999999</v>
+        <v>72.55930000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>30</v>
+        <v>19.4</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.35</v>
+        <v>36.55</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0616</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>17.7</v>
+        <v>13.2</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>77.7</v>
+        <v>83.5</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4716</v>
+        <v>0.5814</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>25.7</v>
+        <v>33.6</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>29.6</v>
+        <v>30.25</v>
       </c>
       <c r="G19" s="38" t="n">
-        <v>0.0034</v>
+        <v>0.0254</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>25.1</v>
+        <v>27.3</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>103.5</v>
+        <v>100.25</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4168</v>
+        <v>0.3723</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>16.2</v>
+        <v>11.3</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-10 05:26</t>
+          <t>2026-06-11 06:30</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.33</v>
+        <v>26.29</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9375</v>
+        <v>0.9345</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>11.8</v>
+        <v>17.7</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>38.34</v>
+        <v>38.17</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.7611</v>
+        <v>0.7533</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>12.6</v>
+        <v>17.7</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>42.5</v>
+        <v>42.55</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.0404</v>
+        <v>0.0416</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>18.8</v>
+        <v>25.1</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>2200</v>
+        <v>2160</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.6541</v>
+        <v>0.6241</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.5498</v>
+        <v>0.5464</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>12.8</v>
+        <v>18.3</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>55.1</v>
+        <v>56.4</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.124</v>
+        <v>-0.1033</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>14.3</v>
+        <v>23.2</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>35.85</v>
-      </c>
-      <c r="G10" s="43" t="n">
-        <v>-0.0218</v>
+        <v>39.4</v>
+      </c>
+      <c r="G10" s="38" t="n">
+        <v>0.075</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>14.7</v>
+        <v>29.4</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.4279</v>
+        <v>-0.4323</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>23.4</v>
+        <v>29.8</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>50.6</v>
+        <v>51.1</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1968</v>
+        <v>-0.1889</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>18.8</v>
+        <v>25.1</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>19.55</v>
+        <v>19.45</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>194.5</v>
+        <v>193.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>20.2</v>
+        <v>26.6</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>122.5</v>
+        <v>125.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.4497</v>
+        <v>0.4852</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>17.3</v>
+        <v>25.8</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>72.55930000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>19.4</v>
+        <v>25.8</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>-0.08169999999999999</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>13.2</v>
+        <v>28.1</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>83.5</v>
+        <v>82</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5814</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>33.6</v>
+        <v>32.6</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>30.25</v>
-      </c>
-      <c r="G19" s="38" t="n">
-        <v>0.0254</v>
+        <v>29.25</v>
+      </c>
+      <c r="G19" s="43" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>27.3</v>
+        <v>21.1</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>100.25</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.3723</v>
+        <v>0.3669</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>11.3</v>
+        <v>19</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-11 06:30</t>
+          <t>2026-06-12 06:25</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -925,7 +925,7 @@
         <v>0.9345</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>17.7</v>
+        <v>18.1</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>0.7533</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>17.7</v>
+        <v>18.1</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>0.0416</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>0.6241</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>0.5464</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>18.3</v>
+        <v>19.1</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>-0.1033</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>23.2</v>
+        <v>23.6</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>0.075</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>29.4</v>
+        <v>29.8</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>-0.4323</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>29.8</v>
+        <v>30.2</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>-0.1889</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>193.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>26.6</v>
+        <v>27.1</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>0.4852</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>25.8</v>
+        <v>26.2</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>72.55930000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>25.8</v>
+        <v>26.2</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>-0.08169999999999999</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>28.1</v>
+        <v>28.5</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>0.5529999999999999</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>32.6</v>
+        <v>33</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>-0.008500000000000001</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>0.3669</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-12 06:25</t>
+          <t>2026-06-16 07:08</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -925,7 +925,7 @@
         <v>0.9345</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>18.1</v>
+        <v>15.1</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>0.7533</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>18.1</v>
+        <v>15.1</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>0.0416</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>25.6</v>
+        <v>22.6</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>0.6241</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>0.5464</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>19.1</v>
+        <v>15.7</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>-0.1033</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>23.6</v>
+        <v>20.7</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>0.075</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>29.8</v>
+        <v>26.8</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>-0.4323</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>30.2</v>
+        <v>27.3</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>-0.1889</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>25.6</v>
+        <v>22.6</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>193.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>27.1</v>
+        <v>24.1</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>0.4852</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>26.2</v>
+        <v>23.2</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>72.55930000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>26.2</v>
+        <v>23.2</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>-0.08169999999999999</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>28.5</v>
+        <v>25.6</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>0.5529999999999999</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>-0.008500000000000001</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>21.5</v>
+        <v>18.5</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>0.3669</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>19.4</v>
+        <v>16.4</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-16 07:08</t>
+          <t>2026-06-17 06:36</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.29</v>
+        <v>27.89</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9345</v>
+        <v>1.0522</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>15.1</v>
+        <v>19.8</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>38.17</v>
+        <v>40.61</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.7533</v>
+        <v>0.8654000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>15.1</v>
+        <v>19.8</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>42.55</v>
+        <v>41.7</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.0416</v>
+        <v>0.0208</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>22.6</v>
+        <v>24</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>2160</v>
+        <v>2155</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.6241</v>
+        <v>0.6203</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>15.5</v>
+        <v>16.9</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2250</v>
+        <v>2385</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.5464</v>
+        <v>0.6392</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>15.7</v>
+        <v>19</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>56.4</v>
+        <v>59</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1033</v>
+        <v>-0.062</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>20.7</v>
+        <v>23.4</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="G10" s="38" t="n">
-        <v>0.075</v>
+        <v>36.2</v>
+      </c>
+      <c r="G10" s="43" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>26.8</v>
+        <v>19.8</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.4323</v>
+        <v>-0.4105</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>27.3</v>
+        <v>28.7</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>51.1</v>
+        <v>51.6</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1889</v>
+        <v>-0.181</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>22.6</v>
+        <v>27.9</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>19.45</v>
+        <v>21.85</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>193.5</v>
+        <v>217.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>24.1</v>
+        <v>39.3</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>125.5</v>
+        <v>135.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.4852</v>
+        <v>0.6036</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>23.2</v>
+        <v>20.5</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>43.4</v>
+        <v>45.1</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>72.55930000000001</v>
+        <v>75.44069999999999</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>23.2</v>
+        <v>22.6</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>36.55</v>
+        <v>38.25</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.0389</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>25.6</v>
+        <v>21.9</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>82</v>
+        <v>85.2</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5529999999999999</v>
+        <v>0.6136</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>30</v>
+        <v>26.2</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>29.25</v>
+        <v>28.45</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0356</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>99.84999999999999</v>
+        <v>106</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.3669</v>
+        <v>0.4511</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>16.4</v>
+        <v>19.8</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-17 06:36</t>
+          <t>2026-06-18 06:23</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.89</v>
+        <v>29.38</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0522</v>
+        <v>1.1619</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>19.8</v>
+        <v>18.7</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.61</v>
+        <v>42.64</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8654000000000001</v>
+        <v>0.9587</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>19.8</v>
+        <v>18.7</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>41.7</v>
+        <v>41.1</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.0208</v>
+        <v>0.0061</v>
       </c>
       <c r="H6" s="39" t="n">
         <v>24</v>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>2155</v>
+        <v>2150</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.6203</v>
+        <v>0.6164999999999999</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>16.9</v>
+        <v>18.2</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2385</v>
+        <v>2510</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6392</v>
+        <v>0.7251000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>19</v>
+        <v>20.4</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,22 +1129,22 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>59</v>
-      </c>
-      <c r="G9" s="43" t="n">
-        <v>-0.062</v>
+        <v>69.09999999999999</v>
+      </c>
+      <c r="G9" s="38" t="n">
+        <v>0.09859999999999999</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>23.4</v>
+        <v>21.9</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J9" s="42" t="inlineStr">
-        <is>
-          <t>🔴 停損</t>
+      <c r="J9" s="41" t="inlineStr">
+        <is>
+          <t>🟠 出清</t>
         </is>
       </c>
     </row>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>36.2</v>
+        <v>35.6</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.0123</v>
+        <v>-0.0286</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>19.8</v>
+        <v>16.6</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.5</v>
+        <v>13.45</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.4105</v>
+        <v>-0.4127</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>28.7</v>
+        <v>27.6</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>51.6</v>
+        <v>52.3</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.181</v>
+        <v>-0.1698</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>27.9</v>
+        <v>26.2</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>21.85</v>
+        <v>21.8</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>217.5</v>
+        <v>217</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>39.3</v>
+        <v>28.7</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>135.5</v>
+        <v>138.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.6036</v>
+        <v>0.6391</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>20.5</v>
+        <v>22.6</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>45.1</v>
+        <v>44.75</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>75.44069999999999</v>
+        <v>74.8475</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>22.6</v>
+        <v>23.9</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>38.25</v>
+        <v>39.05</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0389</v>
+        <v>-0.0188</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>21.9</v>
+        <v>28.7</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>85.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.6136</v>
+        <v>0.4943</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>26.2</v>
+        <v>25.3</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>28.45</v>
+        <v>28.95</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0356</v>
+        <v>-0.0186</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>18.1</v>
+        <v>16.6</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>106</v>
+        <v>111.15</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4511</v>
+        <v>0.5216</v>
       </c>
       <c r="H23" s="39" t="n">
         <v>19.8</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-18 06:23</t>
+          <t>2026-06-23 06:23</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -925,7 +925,7 @@
         <v>1.1619</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>18.7</v>
+        <v>16.1</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>0.9587</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>18.7</v>
+        <v>16.1</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>0.0061</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>24</v>
+        <v>21.4</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>0.6164999999999999</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>18.2</v>
+        <v>15.6</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>0.7251000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>20.4</v>
+        <v>17.7</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>21.9</v>
+        <v>19.3</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>-0.0286</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>16.6</v>
+        <v>13.9</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>-0.4127</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>27.6</v>
+        <v>25</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>-0.1698</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>26.2</v>
+        <v>23.5</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>217</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>28.7</v>
+        <v>26.1</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>0.6391</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>22.6</v>
+        <v>19.9</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>74.8475</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>23.9</v>
+        <v>21.2</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>-0.0188</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>28.7</v>
+        <v>26.1</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>0.4943</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>25.3</v>
+        <v>22.7</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>-0.0186</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>16.6</v>
+        <v>13.9</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>0.5216</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>19.8</v>
+        <v>17.1</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-23 06:23</t>
+          <t>2026-06-24 01:24</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>29.38</v>
+        <v>28.84</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.1619</v>
+        <v>1.1221</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>16.1</v>
+        <v>18.3</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>42.64</v>
+        <v>42.1</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9587</v>
+        <v>0.9339</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>16.1</v>
+        <v>17</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="G6" s="38" t="n">
-        <v>0.0061</v>
+        <v>40</v>
+      </c>
+      <c r="G6" s="43" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>21.4</v>
+        <v>23.8</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>2150</v>
+        <v>2080</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.6164999999999999</v>
+        <v>0.5639</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>15.6</v>
+        <v>15.2</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2510</v>
+        <v>2490</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.7251000000000001</v>
+        <v>0.7112999999999999</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,22 +1129,22 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>69.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G9" s="38" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.04769999999999999</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>19.3</v>
+        <v>22.1</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J9" s="41" t="inlineStr">
-        <is>
-          <t>🟠 出清</t>
+      <c r="J9" s="42" t="inlineStr">
+        <is>
+          <t>🔴 停損</t>
         </is>
       </c>
     </row>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>35.6</v>
+        <v>33.8</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.0286</v>
+        <v>-0.07780000000000001</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.45</v>
+        <v>13.95</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.4127</v>
+        <v>-0.3908</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>25</v>
+        <v>29.3</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>52.3</v>
+        <v>51.3</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1698</v>
+        <v>-0.1857</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>21.8</v>
+        <v>22.3</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>26.1</v>
+        <v>27.2</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>138.5</v>
+        <v>137.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.6391</v>
+        <v>0.6272</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>19.9</v>
+        <v>18.8</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>44.75</v>
+        <v>45.2</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>74.8475</v>
+        <v>75.61020000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>39.05</v>
+        <v>37.9</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0188</v>
+        <v>-0.04769999999999999</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>26.1</v>
+        <v>18.5</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>0.4943</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>28.95</v>
+        <v>29</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0186</v>
+        <v>-0.0169</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>111.15</v>
+        <v>110.1</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.5216</v>
+        <v>0.5072</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-24 01:24</t>
+          <t>2026-06-25 01:25</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>28.84</v>
+        <v>28.41</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.1221</v>
+        <v>1.0905</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>18.3</v>
+        <v>24.3</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>42.1</v>
+        <v>41.12</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9339</v>
+        <v>0.8887999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>17</v>
+        <v>24.3</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>40</v>
+        <v>40.55</v>
       </c>
       <c r="G6" s="43" t="n">
-        <v>-0.0208</v>
+        <v>-0.0073</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>23.8</v>
+        <v>26.6</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>2080</v>
+        <v>2000</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.5639</v>
+        <v>0.5038</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>15.2</v>
+        <v>20</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2490</v>
+        <v>2390</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.7112999999999999</v>
+        <v>0.6426000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>17.6</v>
+        <v>19.9</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,22 +1129,22 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>65.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="G9" s="38" t="n">
-        <v>0.04769999999999999</v>
+        <v>0.1002</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>22.1</v>
+        <v>32.6</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J9" s="42" t="inlineStr">
-        <is>
-          <t>🔴 停損</t>
+      <c r="J9" s="41" t="inlineStr">
+        <is>
+          <t>🟠 出清</t>
         </is>
       </c>
     </row>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>33.8</v>
+        <v>34.3</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.07780000000000001</v>
+        <v>-0.0641</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>14.9</v>
+        <v>17.7</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.95</v>
+        <v>14</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3908</v>
+        <v>-0.3886</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>29.3</v>
+        <v>30.9</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>51.3</v>
+        <v>51.6</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1857</v>
+        <v>-0.181</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>23.4</v>
+        <v>29.6</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>22.3</v>
+        <v>23.25</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>222</v>
+        <v>231.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>27.2</v>
+        <v>38.3</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>137.5</v>
+        <v>134.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.6272</v>
+        <v>0.5917</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>18.8</v>
+        <v>23.7</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>45.2</v>
+        <v>44.55</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>75.61020000000001</v>
+        <v>74.5085</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>20.9</v>
+        <v>22.8</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.9</v>
+        <v>37.75</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.04769999999999999</v>
+        <v>-0.0515</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>18.5</v>
+        <v>20.7</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>78.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4943</v>
+        <v>0.5</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>22.3</v>
+        <v>26.6</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>29</v>
+        <v>28.65</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0169</v>
+        <v>-0.0288</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>14.9</v>
+        <v>19.2</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>110.1</v>
+        <v>107.15</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.5072</v>
+        <v>0.4668</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>17</v>
+        <v>24.3</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-25 01:25</t>
+          <t>2026-06-26 01:28</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>28.41</v>
+        <v>27.05</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0905</v>
+        <v>0.9904000000000001</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>24.3</v>
+        <v>19.8</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>41.12</v>
+        <v>39.57</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8887999999999999</v>
+        <v>0.8176000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>24.3</v>
+        <v>19.8</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>40.55</v>
+        <v>39.9</v>
       </c>
       <c r="G6" s="43" t="n">
-        <v>-0.0073</v>
+        <v>-0.0233</v>
       </c>
       <c r="H6" s="39" t="n">
         <v>26.6</v>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>2000</v>
+        <v>1810</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.5038</v>
+        <v>0.3609000000000001</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>20</v>
+        <v>21.7</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2390</v>
+        <v>2340</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6426000000000001</v>
+        <v>0.6082</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>19.9</v>
+        <v>21.1</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>69.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G9" s="38" t="n">
-        <v>0.1002</v>
+        <v>0.0906</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>32.6</v>
+        <v>29.4</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>34.3</v>
+        <v>34.55</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.0641</v>
+        <v>-0.0573</v>
       </c>
       <c r="H10" s="39" t="n">
         <v>17.7</v>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3886</v>
+        <v>-0.4017</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>30.9</v>
+        <v>26.6</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>51.6</v>
+        <v>50.1</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.181</v>
+        <v>-0.2048</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>29.6</v>
+        <v>25.1</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>23.25</v>
+        <v>23.2</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>231.5</v>
+        <v>231</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>38.3</v>
+        <v>28.8</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>134.5</v>
+        <v>134</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.5917</v>
+        <v>0.5858</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>23.7</v>
+        <v>21.6</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>44.55</v>
+        <v>46.15</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>74.5085</v>
+        <v>77.22029999999999</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.75</v>
+        <v>37.5</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0515</v>
+        <v>-0.0578</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>20.7</v>
+        <v>23.2</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>79.2</v>
+        <v>78.7</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5</v>
+        <v>0.4905</v>
       </c>
       <c r="H17" s="39" t="n">
         <v>26.6</v>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>28.65</v>
+        <v>28.25</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0288</v>
+        <v>-0.0424</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>19.2</v>
+        <v>20.7</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>107.15</v>
+        <v>103.1</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4668</v>
+        <v>0.4114</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>24.3</v>
+        <v>20.5</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-26 01:28</t>
+          <t>2026-06-30 01:57</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.05</v>
+        <v>27.4</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9904000000000001</v>
+        <v>1.0162</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>19.8</v>
+        <v>19.2</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>39.57</v>
+        <v>40</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8176000000000001</v>
+        <v>0.8373999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>19.8</v>
+        <v>19.2</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>39.9</v>
+        <v>40.4</v>
       </c>
       <c r="G6" s="43" t="n">
-        <v>-0.0233</v>
+        <v>-0.011</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>26.6</v>
+        <v>32.6</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1810</v>
+        <v>1905</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3609000000000001</v>
+        <v>0.4323</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>21.7</v>
+        <v>21.2</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2340</v>
+        <v>2370</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6082</v>
+        <v>0.6289</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>21.1</v>
+        <v>20.2</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>68.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="G9" s="38" t="n">
-        <v>0.0906</v>
+        <v>0.0922</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>29.4</v>
+        <v>23</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>34.55</v>
-      </c>
-      <c r="G10" s="43" t="n">
-        <v>-0.0573</v>
+        <v>38</v>
+      </c>
+      <c r="G10" s="38" t="n">
+        <v>0.0368</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>17.7</v>
+        <v>22.6</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.7</v>
+        <v>13.75</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.4017</v>
+        <v>-0.3996</v>
       </c>
       <c r="H11" s="39" t="n">
         <v>26.6</v>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>50.1</v>
+        <v>51.4</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.2048</v>
+        <v>-0.1841</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>25.1</v>
+        <v>27.9</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>28.8</v>
+        <v>26.6</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>134</v>
+        <v>128.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.5858</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>21.6</v>
+        <v>25.1</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>46.15</v>
+        <v>46.2</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>77.22029999999999</v>
+        <v>77.3051</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>23.7</v>
+        <v>21.6</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.5</v>
+        <v>37.65</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0578</v>
+        <v>-0.05400000000000001</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>23.2</v>
+        <v>20.7</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4905</v>
+        <v>0.4867</v>
       </c>
       <c r="H17" s="39" t="n">
         <v>26.6</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>28.25</v>
+        <v>27.65</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0424</v>
+        <v>-0.06269999999999999</v>
       </c>
       <c r="H19" s="39" t="n">
         <v>20.7</v>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>103.1</v>
+        <v>104.45</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4114</v>
+        <v>0.4298</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>20.5</v>
+        <v>19.2</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-06-30 01:57</t>
+          <t>2026-07-01 01:20</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.4</v>
+        <v>28.46</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0162</v>
+        <v>1.0942</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>19.2</v>
+        <v>20.5</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40</v>
+        <v>41.25</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8373999999999999</v>
+        <v>0.8948</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>19.2</v>
+        <v>20.5</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>40.4</v>
+        <v>40.35</v>
       </c>
       <c r="G6" s="43" t="n">
-        <v>-0.011</v>
+        <v>-0.0122</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>32.6</v>
+        <v>30</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1905</v>
+        <v>1950</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.4323</v>
+        <v>0.4661999999999999</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2370</v>
+        <v>2410</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6289</v>
+        <v>0.6564</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>20.2</v>
+        <v>21.1</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>68.7</v>
+        <v>69</v>
       </c>
       <c r="G9" s="38" t="n">
-        <v>0.0922</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,22 +1171,22 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>38</v>
+        <v>41.8</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>0.0368</v>
+        <v>0.1405</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>22.6</v>
+        <v>29.6</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J10" s="42" t="inlineStr">
-        <is>
-          <t>🔴 停損</t>
+      <c r="J10" s="41" t="inlineStr">
+        <is>
+          <t>🟠 出清</t>
         </is>
       </c>
     </row>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.75</v>
+        <v>13.8</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3996</v>
+        <v>-0.3974</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>26.6</v>
+        <v>25.6</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>51.4</v>
+        <v>52</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1841</v>
+        <v>-0.1746</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>27.9</v>
+        <v>26.4</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>26.6</v>
+        <v>26.2</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>128.5</v>
+        <v>129.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5325</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>25.1</v>
+        <v>23.6</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>77.3051</v>
+        <v>77.13560000000001</v>
       </c>
       <c r="H15" s="39" t="n">
         <v>21.6</v>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.65</v>
+        <v>38</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.05400000000000001</v>
+        <v>-0.0452</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>78.5</v>
+        <v>78.3</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4867</v>
+        <v>0.483</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>26.6</v>
+        <v>24.1</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>27.65</v>
+        <v>27.9</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.06269999999999999</v>
+        <v>-0.0542</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>20.7</v>
+        <v>18.1</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>104.45</v>
+        <v>107.8</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4298</v>
+        <v>0.4757</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>19.2</v>
+        <v>20.5</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-01 01:20</t>
+          <t>2026-07-02 01:27</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>28.46</v>
+        <v>28.73</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0942</v>
+        <v>1.1141</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>20.5</v>
+        <v>19.2</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>41.25</v>
+        <v>41.91</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8948</v>
+        <v>0.9251</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>20.5</v>
+        <v>19.2</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>40.35</v>
-      </c>
-      <c r="G6" s="43" t="n">
-        <v>-0.0122</v>
+        <v>41.5</v>
+      </c>
+      <c r="G6" s="38" t="n">
+        <v>0.0159</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>30</v>
+        <v>34.7</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1950</v>
+        <v>1990</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.4661999999999999</v>
+        <v>0.4962</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>21.4</v>
+        <v>18.7</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2410</v>
+        <v>2505</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6564</v>
+        <v>0.7216</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>21.1</v>
+        <v>19.4</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>69</v>
+        <v>73.5</v>
       </c>
       <c r="G9" s="38" t="n">
-        <v>0.09699999999999999</v>
+        <v>0.1685</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>21.7</v>
+        <v>29.8</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>41.8</v>
+        <v>40.2</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>0.1405</v>
+        <v>0.0969</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>29.6</v>
+        <v>20.2</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>-0.3974</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>25.6</v>
+        <v>24.3</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>52</v>
+        <v>50.7</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1746</v>
+        <v>-0.1952</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>26.4</v>
+        <v>21.3</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>23.7</v>
+        <v>22.55</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>236</v>
+        <v>224.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>26.2</v>
+        <v>25.6</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>129.5</v>
+        <v>122.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.5325</v>
+        <v>0.4497</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>23.6</v>
+        <v>21.1</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>46.1</v>
+        <v>46.15</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>77.13560000000001</v>
+        <v>77.22029999999999</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>21.6</v>
+        <v>25.2</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>38</v>
+        <v>37.7</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0452</v>
+        <v>-0.0528</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>20.9</v>
+        <v>16.9</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>78.3</v>
+        <v>79</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.483</v>
+        <v>0.4962</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>24.1</v>
+        <v>25.6</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>27.9</v>
+        <v>27</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0542</v>
+        <v>-0.08470000000000001</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>107.8</v>
+        <v>109.35</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4757</v>
+        <v>0.4969</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>20.5</v>
+        <v>19.2</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-02 01:27</t>
+          <t>2026-07-03 01:08</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>28.73</v>
+        <v>28.7</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.1141</v>
+        <v>1.1118</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>19.2</v>
+        <v>33.2</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>41.91</v>
+        <v>41.76</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9251</v>
+        <v>0.9181999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>19.2</v>
+        <v>31.9</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>41.5</v>
+        <v>41.15</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.0159</v>
+        <v>0.0073</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>34.7</v>
+        <v>24</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1990</v>
+        <v>2075</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.4962</v>
+        <v>0.5602</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>18.7</v>
+        <v>18</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2505</v>
+        <v>2445</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.7216</v>
+        <v>0.6804000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>19.4</v>
+        <v>24.2</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>73.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G9" s="38" t="n">
-        <v>0.1685</v>
+        <v>0.1224</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>29.8</v>
+        <v>23.6</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>40.2</v>
+        <v>41.15</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>0.0969</v>
+        <v>0.1228</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>20.2</v>
+        <v>22.1</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3974</v>
+        <v>-0.3843</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>24.3</v>
+        <v>31</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>50.7</v>
+        <v>52.4</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1952</v>
+        <v>-0.1683</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>21.3</v>
+        <v>29.6</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>224.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>25.6</v>
+        <v>29.3</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>122.5</v>
+        <v>121</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.4497</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>21.1</v>
+        <v>23.6</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>46.15</v>
+        <v>45.5</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>77.22029999999999</v>
+        <v>76.1186</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>25.2</v>
+        <v>22.2</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.7</v>
+        <v>38.2</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0528</v>
+        <v>-0.04019999999999999</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>16.9</v>
+        <v>20.2</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>79</v>
+        <v>80.5</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4962</v>
+        <v>0.5246</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>25.6</v>
+        <v>31</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>27</v>
+        <v>28.35</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.08470000000000001</v>
+        <v>-0.039</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>17.7</v>
+        <v>32.5</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>109.35</v>
+        <v>108.35</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4969</v>
+        <v>0.4832</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>19.2</v>
+        <v>31.9</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-03 01:08</t>
+          <t>2026-07-07 01:57</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>28.7</v>
+        <v>28.61</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.1118</v>
+        <v>1.1052</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>33.2</v>
+        <v>28.9</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>41.76</v>
+        <v>41.57</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9181999999999999</v>
+        <v>0.9095</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>31.9</v>
+        <v>26.4</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>41.15</v>
+        <v>41.3</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.0073</v>
+        <v>0.011</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>24</v>
+        <v>21.9</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>2075</v>
+        <v>1995</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.5602</v>
+        <v>0.5</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>18</v>
+        <v>14.2</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2445</v>
+        <v>2460</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6804000000000001</v>
+        <v>0.6907</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>24.2</v>
+        <v>20.4</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>70.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="G9" s="38" t="n">
-        <v>0.1224</v>
+        <v>0.0859</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>23.6</v>
+        <v>17.7</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>41.15</v>
+        <v>41.45</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>0.1228</v>
+        <v>0.131</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>22.1</v>
+        <v>19.4</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3843</v>
+        <v>-0.3886</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>31</v>
+        <v>28.8</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>52.4</v>
+        <v>53</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1683</v>
+        <v>-0.1587</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>29.6</v>
+        <v>24.7</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>22.55</v>
+        <v>22.45</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>224.5</v>
+        <v>223.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>29.3</v>
+        <v>26.6</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>121</v>
+        <v>121.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.4379</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>23.6</v>
+        <v>20.9</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>45.5</v>
+        <v>46.3</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>76.1186</v>
+        <v>77.4746</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>22.2</v>
+        <v>21.6</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>38.2</v>
+        <v>38.15</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.04019999999999999</v>
+        <v>-0.0415</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>20.2</v>
+        <v>16.4</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>80.5</v>
+        <v>80.3</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5246</v>
+        <v>0.5207999999999999</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>31</v>
+        <v>27.3</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>28.35</v>
+        <v>28.6</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.039</v>
+        <v>-0.0305</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>32.5</v>
+        <v>17.7</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>108.35</v>
+        <v>108.25</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4832</v>
+        <v>0.4819</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>31.9</v>
+        <v>26.4</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-07 01:57</t>
+          <t>2026-07-08 01:31</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>28.61</v>
+        <v>27.67</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.1052</v>
+        <v>1.0361</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>28.9</v>
+        <v>22.3</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>41.57</v>
+        <v>40.53</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9095</v>
+        <v>0.8617</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>26.4</v>
+        <v>27</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>41.3</v>
+        <v>40.9</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.011</v>
+        <v>0.0012</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>21.9</v>
+        <v>26.2</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1995</v>
+        <v>1890</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.5</v>
+        <v>0.4211</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>14.2</v>
+        <v>18</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2460</v>
+        <v>2440</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6907</v>
+        <v>0.677</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>20.4</v>
+        <v>21</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,22 +1129,22 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>68.3</v>
+        <v>65.7</v>
       </c>
       <c r="G9" s="38" t="n">
-        <v>0.0859</v>
+        <v>0.0445</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>17.7</v>
+        <v>21.9</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J9" s="41" t="inlineStr">
-        <is>
-          <t>🟠 出清</t>
+      <c r="J9" s="42" t="inlineStr">
+        <is>
+          <t>🔴 停損</t>
         </is>
       </c>
     </row>
@@ -1171,22 +1171,22 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>41.45</v>
+        <v>39.1</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>0.131</v>
+        <v>0.0668</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>19.4</v>
+        <v>18.9</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J10" s="41" t="inlineStr">
-        <is>
-          <t>🟠 出清</t>
+      <c r="J10" s="42" t="inlineStr">
+        <is>
+          <t>🔴 停損</t>
         </is>
       </c>
     </row>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14</v>
+        <v>13.85</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3886</v>
+        <v>-0.3952000000000001</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>28.8</v>
+        <v>29.3</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>53</v>
+        <v>51.1</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1587</v>
+        <v>-0.1889</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>24.7</v>
+        <v>24</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>22.45</v>
+        <v>22</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>223.5</v>
+        <v>219</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>26.6</v>
+        <v>29.3</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>121.5</v>
+        <v>123</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.4379</v>
+        <v>0.4556</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>20.9</v>
+        <v>23.6</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>46.3</v>
+        <v>46.8</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>77.4746</v>
+        <v>78.322</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>21.6</v>
+        <v>28.5</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>38.15</v>
+        <v>37.3</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0415</v>
+        <v>-0.06280000000000001</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>16.4</v>
+        <v>19.1</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>80.3</v>
+        <v>79.3</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5207999999999999</v>
+        <v>0.5019</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>27.3</v>
+        <v>27.9</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>28.6</v>
+        <v>27.8</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0305</v>
+        <v>-0.0576</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>17.7</v>
+        <v>19.1</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>108.25</v>
+        <v>106.2</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4819</v>
+        <v>0.4538</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>26.4</v>
+        <v>27</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-08 01:31</t>
+          <t>2026-07-09 00:55</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.67</v>
+        <v>27.49</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0361</v>
+        <v>1.0228</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>22.3</v>
+        <v>23.1</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.53</v>
+        <v>40.48</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8617</v>
+        <v>0.8593999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>27</v>
+        <v>23.3</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="G6" s="38" t="n">
-        <v>0.0012</v>
+        <v>40.55</v>
+      </c>
+      <c r="G6" s="43" t="n">
+        <v>-0.0073</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>26.2</v>
+        <v>27.7</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1890</v>
+        <v>1885</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.4211</v>
+        <v>0.4172999999999999</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>18</v>
+        <v>19.1</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2440</v>
+        <v>2465</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.677</v>
+        <v>0.6942</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>21</v>
+        <v>24.2</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>65.7</v>
+        <v>67</v>
       </c>
       <c r="G9" s="38" t="n">
-        <v>0.0445</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>21.9</v>
+        <v>23</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>39.1</v>
+        <v>39.05</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>0.0668</v>
+        <v>0.0655</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>18.9</v>
+        <v>21.5</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.85</v>
+        <v>13.75</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3952000000000001</v>
+        <v>-0.3996</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>29.3</v>
+        <v>30.4</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>51.1</v>
+        <v>52.3</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1889</v>
+        <v>-0.1698</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>24</v>
+        <v>28.5</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>22</v>
+        <v>22.05</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>219</v>
+        <v>219.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>29.3</v>
+        <v>28.3</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.4556</v>
+        <v>0.4911</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>23.6</v>
+        <v>29.2</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>78.322</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>28.5</v>
+        <v>27.5</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.3</v>
+        <v>37.6</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.06280000000000001</v>
+        <v>-0.0553</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>19.1</v>
+        <v>20.2</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5019</v>
+        <v>0.5</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>27.9</v>
+        <v>29</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>27.8</v>
+        <v>27.3</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0576</v>
+        <v>-0.0746</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>19.1</v>
+        <v>20.2</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>106.2</v>
+        <v>106.05</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4538</v>
+        <v>0.4517</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>27</v>
+        <v>26.3</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-09 00:55</t>
+          <t>2026-07-10 01:29</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.49</v>
+        <v>27.55</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0228</v>
+        <v>1.0272</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>23.1</v>
+        <v>15.9</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.48</v>
+        <v>40.39</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8593999999999999</v>
+        <v>0.8553000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>23.3</v>
+        <v>15.9</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>40.55</v>
+        <v>40</v>
       </c>
       <c r="G6" s="43" t="n">
-        <v>-0.0073</v>
+        <v>-0.0208</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>27.7</v>
+        <v>21.9</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1885</v>
+        <v>1880</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.4172999999999999</v>
+        <v>0.4135</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>19.1</v>
+        <v>13.4</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2465</v>
+        <v>2415</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6942</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>24.2</v>
+        <v>17.4</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>67</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G9" s="38" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0429</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>23</v>
+        <v>18.3</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>39.05</v>
+        <v>38.5</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>0.0655</v>
+        <v>0.0505</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>21.5</v>
+        <v>16.9</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.75</v>
+        <v>13.65</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3996</v>
+        <v>-0.4039</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>30.4</v>
+        <v>25.8</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>52.3</v>
+        <v>51.6</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1698</v>
+        <v>-0.181</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>28.5</v>
+        <v>20.5</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>22.05</v>
+        <v>21.4</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>219.5</v>
+        <v>213</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>28.3</v>
+        <v>23</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>126</v>
+        <v>124.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.4911</v>
+        <v>0.4734</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>29.2</v>
+        <v>21.7</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>78.322</v>
+        <v>78.1525</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>27.5</v>
+        <v>23.9</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0553</v>
+        <v>-0.0578</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>20.2</v>
+        <v>15.6</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>0.5</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>29</v>
+        <v>24.3</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>27.3</v>
+        <v>27</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0746</v>
+        <v>-0.08470000000000001</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>20.2</v>
+        <v>16.9</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>106.05</v>
+        <v>105.8</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4517</v>
+        <v>0.4483</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>26.3</v>
+        <v>18.8</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-10 01:29</t>
+          <t>2026-07-14 01:27</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.55</v>
+        <v>27.39</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0272</v>
+        <v>1.0155</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>15.9</v>
+        <v>22.2</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.39</v>
+        <v>40.35</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8553000000000001</v>
+        <v>0.8534999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>15.9</v>
+        <v>19.9</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>40</v>
+        <v>39.5</v>
       </c>
       <c r="G6" s="43" t="n">
-        <v>-0.0208</v>
+        <v>-0.033</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>21.9</v>
+        <v>27.1</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1880</v>
+        <v>1890</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.4135</v>
+        <v>0.4211</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>13.4</v>
+        <v>18.5</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2415</v>
+        <v>2440</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.677</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>17.4</v>
+        <v>22.5</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>65.59999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="G9" s="38" t="n">
-        <v>0.0429</v>
+        <v>0.0413</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>18.3</v>
+        <v>23.4</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>38.5</v>
+        <v>37.15</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>0.0505</v>
+        <v>0.0136</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>16.9</v>
+        <v>19.2</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.65</v>
+        <v>13.7</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.4039</v>
+        <v>-0.4017</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>25.8</v>
+        <v>30.9</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>51.6</v>
+        <v>50.1</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.181</v>
+        <v>-0.2048</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>20.5</v>
+        <v>25.6</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>21.4</v>
+        <v>21.05</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>213</v>
+        <v>209.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>23</v>
+        <v>27.1</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>124.5</v>
+        <v>127</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.4734</v>
+        <v>0.503</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>21.7</v>
+        <v>27.9</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>46.7</v>
+        <v>47</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>78.1525</v>
+        <v>78.661</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>23.9</v>
+        <v>27.9</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.5</v>
+        <v>38.1</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0578</v>
+        <v>-0.04269999999999999</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>15.6</v>
+        <v>25.6</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5</v>
+        <v>0.5038</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>24.3</v>
+        <v>27.9</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>27</v>
+        <v>26.55</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.08470000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>16.9</v>
+        <v>22.6</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>105.8</v>
+        <v>106</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4483</v>
+        <v>0.4511</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>18.8</v>
+        <v>26.7</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-14 01:27</t>
+          <t>2026-07-15 00:42</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.39</v>
+        <v>26.83</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0155</v>
+        <v>0.9742000000000001</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>22.2</v>
+        <v>16.1</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.35</v>
+        <v>39.65</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8534999999999999</v>
+        <v>0.8212999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
         <v>19.9</v>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>39.5</v>
+        <v>39.1</v>
       </c>
       <c r="G6" s="43" t="n">
-        <v>-0.033</v>
+        <v>-0.0428</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>27.1</v>
+        <v>23.9</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1890</v>
+        <v>1855</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.4211</v>
+        <v>0.3947</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>18.5</v>
+        <v>14.2</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2440</v>
+        <v>2420</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.677</v>
+        <v>0.6631999999999999</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>22.5</v>
+        <v>16.2</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="G9" s="38" t="n">
-        <v>0.0413</v>
+        <v>62.1</v>
+      </c>
+      <c r="G9" s="43" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>23.4</v>
+        <v>15.4</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>37.15</v>
-      </c>
-      <c r="G10" s="38" t="n">
-        <v>0.0136</v>
+        <v>34.85</v>
+      </c>
+      <c r="G10" s="43" t="n">
+        <v>-0.0491</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>19.2</v>
+        <v>13.9</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.7</v>
+        <v>14.5</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.4017</v>
+        <v>-0.3668</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>30.9</v>
+        <v>42.8</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>50.1</v>
+        <v>48</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.2048</v>
+        <v>-0.2381</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>25.6</v>
+        <v>21.3</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>21.05</v>
+        <v>20.4</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>209.5</v>
+        <v>203</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>27.1</v>
+        <v>22.8</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.503</v>
+        <v>0.4793</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>27.9</v>
+        <v>20.9</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>78.661</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>27.9</v>
+        <v>24.8</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>38.1</v>
+        <v>37.5</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.04269999999999999</v>
+        <v>-0.0578</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>25.6</v>
+        <v>21.1</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>0.5038</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>27.9</v>
+        <v>21.3</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.55</v>
+        <v>26.05</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1</v>
+        <v>-0.1169</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>22.6</v>
+        <v>17.7</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>106</v>
+        <v>104.4</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4511</v>
+        <v>0.4292</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>26.7</v>
+        <v>18.2</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-15 00:42</t>
+          <t>2026-07-16 00:49</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.83</v>
+        <v>27.56</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9742000000000001</v>
+        <v>1.028</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>16.1</v>
+        <v>19.8</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>39.65</v>
+        <v>40.39</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8212999999999999</v>
+        <v>0.8553000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>19.9</v>
+        <v>18.5</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="G6" s="43" t="n">
-        <v>-0.0428</v>
+        <v>41.3</v>
+      </c>
+      <c r="G6" s="38" t="n">
+        <v>0.011</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>23.9</v>
+        <v>28.5</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1855</v>
+        <v>1890</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3947</v>
+        <v>0.4211</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>14.2</v>
+        <v>15.5</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2420</v>
+        <v>2440</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6631999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>16.2</v>
+        <v>19</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="G9" s="43" t="n">
-        <v>-0.0127</v>
+        <v>65</v>
+      </c>
+      <c r="G9" s="38" t="n">
+        <v>0.0334</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>15.4</v>
+        <v>19.8</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>34.85</v>
+        <v>35</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.0491</v>
+        <v>-0.045</v>
       </c>
       <c r="H10" s="39" t="n">
         <v>13.9</v>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.5</v>
+        <v>13.85</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3668</v>
+        <v>-0.3952000000000001</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>42.8</v>
+        <v>27.7</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>48</v>
+        <v>50.2</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.2381</v>
+        <v>-0.2032</v>
       </c>
       <c r="H12" s="39" t="n">
         <v>21.3</v>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.4</v>
+        <v>21.2</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>22.8</v>
+        <v>27.1</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>125</v>
+        <v>128.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.4793</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>20.9</v>
+        <v>23.2</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>78.661</v>
+        <v>76.9661</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>24.8</v>
+        <v>19.4</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0578</v>
+        <v>-0.0452</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>21.1</v>
+        <v>26.6</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>79.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5038</v>
+        <v>0.5189</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>21.3</v>
+        <v>24.7</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.05</v>
+        <v>26.45</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1169</v>
+        <v>-0.1034</v>
       </c>
       <c r="H19" s="39" t="n">
         <v>17.7</v>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>104.4</v>
+        <v>106.3</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4292</v>
+        <v>0.4552</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>18.2</v>
+        <v>24.2</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-16 00:49</t>
+          <t>2026-07-17 00:47</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.56</v>
+        <v>24.62</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.028</v>
+        <v>0.8116</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>19.8</v>
+        <v>18.8</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.39</v>
+        <v>37.91</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8553000000000001</v>
+        <v>0.7414000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>18.5</v>
+        <v>20.5</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="G6" s="38" t="n">
-        <v>0.011</v>
+        <v>40.65</v>
+      </c>
+      <c r="G6" s="43" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>28.5</v>
+        <v>27.6</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1890</v>
+        <v>1740</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.4211</v>
+        <v>0.3083</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>15.5</v>
+        <v>16.9</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2440</v>
+        <v>2290</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.677</v>
+        <v>0.5739</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>65</v>
-      </c>
-      <c r="G9" s="38" t="n">
-        <v>0.0334</v>
+        <v>56.7</v>
+      </c>
+      <c r="G9" s="43" t="n">
+        <v>-0.09859999999999999</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>35</v>
+        <v>30.75</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.045</v>
+        <v>-0.161</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>13.9</v>
+        <v>18.1</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.85</v>
+        <v>13.9</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3952000000000001</v>
+        <v>-0.393</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>27.7</v>
+        <v>25.7</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>50.2</v>
+        <v>49.2</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.2032</v>
+        <v>-0.219</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>21.3</v>
+        <v>24</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>21.2</v>
+        <v>20.75</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>211</v>
+        <v>206.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>27.1</v>
+        <v>28.7</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>128.5</v>
+        <v>124.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.4734</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>23.2</v>
+        <v>22.5</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>46</v>
+        <v>47.6</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>76.9661</v>
+        <v>79.678</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>19.4</v>
+        <v>30.9</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>38</v>
+        <v>38.65</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0452</v>
+        <v>-0.0289</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>26.6</v>
+        <v>29.3</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>80.2</v>
+        <v>81.2</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5189</v>
+        <v>0.5379</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>24.7</v>
+        <v>31</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.45</v>
+        <v>25.85</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1034</v>
+        <v>-0.1237</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>17.7</v>
+        <v>20.5</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>106.3</v>
+        <v>100.15</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4552</v>
+        <v>0.371</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>24.2</v>
+        <v>22.6</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-17 00:47</t>
+          <t>2026-07-21 00:51</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>24.62</v>
+        <v>24.02</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.8116</v>
+        <v>0.7675</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>37.91</v>
+        <v>37.5</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.7414000000000001</v>
+        <v>0.7226</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>20.5</v>
+        <v>21.8</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>40.65</v>
+        <v>40.45</v>
       </c>
       <c r="G6" s="43" t="n">
-        <v>-0.0049</v>
+        <v>-0.0098</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>27.6</v>
+        <v>28.8</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1740</v>
+        <v>1705</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3083</v>
+        <v>0.282</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>16.9</v>
+        <v>18</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2290</v>
+        <v>2320</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.5739</v>
+        <v>0.5945</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>-0.09859999999999999</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>19.6</v>
+        <v>20.7</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>30.75</v>
+        <v>30.25</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.161</v>
+        <v>-0.1746</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>18.1</v>
+        <v>19.2</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.9</v>
+        <v>13.95</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.393</v>
+        <v>-0.3908</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>25.7</v>
+        <v>27.9</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.219</v>
+        <v>-0.2222</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.75</v>
+        <v>20.95</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>206.5</v>
+        <v>208.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>28.7</v>
+        <v>29.4</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>124.5</v>
+        <v>123.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.4734</v>
+        <v>0.4615</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>22.5</v>
+        <v>23.6</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>47.6</v>
+        <v>48.2</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>79.678</v>
+        <v>80.6949</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>30.9</v>
+        <v>29.6</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>38.65</v>
+        <v>37.2</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0289</v>
+        <v>-0.0653</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>29.3</v>
+        <v>19.8</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>81.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5379</v>
+        <v>0.5265</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>31</v>
+        <v>32.1</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>25.85</v>
+        <v>25.8</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1237</v>
+        <v>-0.1254</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>20.5</v>
+        <v>23.7</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>100.15</v>
+        <v>99.2</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.371</v>
+        <v>0.358</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>22.6</v>
+        <v>23.7</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-21 00:51</t>
+          <t>2026-07-22 00:52</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>24.02</v>
+        <v>25.15</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.7675</v>
+        <v>0.8506</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>20.8</v>
+        <v>28</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>37.5</v>
+        <v>39.06</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.7226</v>
+        <v>0.7942</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>21.8</v>
+        <v>29.5</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>40.45</v>
-      </c>
-      <c r="G6" s="43" t="n">
-        <v>-0.0098</v>
+        <v>41.15</v>
+      </c>
+      <c r="G6" s="38" t="n">
+        <v>0.0073</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>28.8</v>
+        <v>37.2</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1705</v>
+        <v>1835</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.282</v>
+        <v>0.3797</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>18</v>
+        <v>27.4</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2320</v>
+        <v>2410</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.5945</v>
+        <v>0.6564</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>19.6</v>
+        <v>28.4</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>56.7</v>
+        <v>57.4</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>20.7</v>
+        <v>28.5</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>30.25</v>
+        <v>32.1</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1746</v>
+        <v>-0.1241</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>19.2</v>
+        <v>28.2</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.95</v>
+        <v>14</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3908</v>
+        <v>-0.3886</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>27.9</v>
+        <v>33.5</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>49</v>
+        <v>50.9</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.2222</v>
+        <v>-0.1921</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>25.1</v>
+        <v>32.3</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.95</v>
+        <v>21.45</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>208.5</v>
+        <v>213.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>29.4</v>
+        <v>32.6</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>0.4615</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>23.6</v>
+        <v>30.5</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>48.2</v>
+        <v>48.6</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>80.6949</v>
+        <v>81.3729</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>29.6</v>
+        <v>36.2</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.2</v>
+        <v>37.5</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0653</v>
+        <v>-0.0578</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>19.8</v>
+        <v>27.8</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>80.59999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5265</v>
+        <v>0.5322</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>32.1</v>
+        <v>38.8</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>25.8</v>
+        <v>26.4</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1254</v>
+        <v>-0.1051</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>23.7</v>
+        <v>32</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>99.2</v>
+        <v>102.5</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.358</v>
+        <v>0.4031</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>23.7</v>
+        <v>29.5</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-22 00:52</t>
+          <t>2026-07-23 00:54</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="新細明體"/>
       <family val="2"/>
@@ -172,8 +172,14 @@
       <color rgb="00888888"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -270,6 +276,11 @@
         <fgColor rgb="00FDEDEC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F3F4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -313,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -443,6 +454,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -919,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>25.15</v>
+        <v>25.7</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.8506</v>
+        <v>0.8911</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>28</v>
+        <v>28.8</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -961,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>39.06</v>
+        <v>39.8</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.7942</v>
+        <v>0.8281999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>29.5</v>
+        <v>28.6</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1003,22 +1017,22 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>41.15</v>
+        <v>43.75</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.0073</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>37.2</v>
+        <v>47.3</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J6" s="42" t="inlineStr">
-        <is>
-          <t>🔴 停損</t>
+      <c r="J6" s="45" t="inlineStr">
+        <is>
+          <t>⚪ 觀察</t>
         </is>
       </c>
     </row>
@@ -1045,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1835</v>
+        <v>1880</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3797</v>
+        <v>0.4135</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>27.4</v>
+        <v>29.8</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1087,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6564</v>
+        <v>0.6495000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>28.4</v>
+        <v>27</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1129,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>57.4</v>
+        <v>59</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.062</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>28.5</v>
+        <v>29.6</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1171,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>32.1</v>
+        <v>35.3</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1241</v>
+        <v>-0.0368</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>28.2</v>
+        <v>27.4</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1213,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3886</v>
+        <v>-0.393</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>33.5</v>
+        <v>33.8</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1255,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>50.9</v>
+        <v>51.4</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1921</v>
+        <v>-0.1841</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>32.3</v>
+        <v>35.3</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1297,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>21.45</v>
+        <v>21.35</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>213.5</v>
+        <v>212.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1339,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>123.5</v>
+        <v>127</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.4615</v>
+        <v>0.503</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>30.5</v>
+        <v>31.2</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1381,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>48.6</v>
+        <v>48.2</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>81.3729</v>
+        <v>80.6949</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>36.2</v>
+        <v>33.5</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1423,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.5</v>
+        <v>37.15</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0578</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>27.8</v>
+        <v>28.1</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1465,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>80.90000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5322</v>
+        <v>0.5133</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>38.8</v>
+        <v>33</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1531,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1051</v>
+        <v>-0.1186</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>32</v>
+        <v>32.3</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1645,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>102.5</v>
+        <v>103.85</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4031</v>
+        <v>0.4216</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>29.5</v>
+        <v>28.6</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1794,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-23 00:54</t>
+          <t>2026-07-24 00:53</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -939,7 +939,7 @@
         <v>0.8911</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>28.8</v>
+        <v>27</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>0.8281999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>28.6</v>
+        <v>26.8</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>47.3</v>
+        <v>45.5</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>0.4135</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>29.8</v>
+        <v>28</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>0.6495000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>27</v>
+        <v>25.2</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>-0.062</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>29.6</v>
+        <v>27.8</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>-0.0368</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>27.4</v>
+        <v>25.6</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>-0.393</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>33.8</v>
+        <v>32</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>-0.1841</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>35.3</v>
+        <v>33.5</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>212.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>32.9</v>
+        <v>31.1</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>0.503</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>31.2</v>
+        <v>29.4</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>80.6949</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>33.5</v>
+        <v>31.7</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>-0.06660000000000001</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>28.1</v>
+        <v>26.3</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>0.5133</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>33</v>
+        <v>31.2</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>-0.1186</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>32.3</v>
+        <v>30.5</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>0.4216</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>28.6</v>
+        <v>26.8</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-24 00:53</t>
+          <t>2026-07-28 01:15</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>25.7</v>
+        <v>24.95</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.8911</v>
+        <v>0.8359000000000001</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>27</v>
+        <v>25.4</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>39.8</v>
+        <v>38.97</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8281999999999999</v>
+        <v>0.7901</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>26.8</v>
+        <v>26.5</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,22 +1017,22 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>43.75</v>
+        <v>44.55</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0906</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>45.5</v>
+        <v>35.6</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J6" s="45" t="inlineStr">
-        <is>
-          <t>⚪ 觀察</t>
+      <c r="J6" s="41" t="inlineStr">
+        <is>
+          <t>🟠 出清</t>
         </is>
       </c>
     </row>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1880</v>
+        <v>1755</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.4135</v>
+        <v>0.3195</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>28</v>
+        <v>25.2</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2400</v>
+        <v>2350</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6495000000000001</v>
+        <v>0.6151</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>25.2</v>
+        <v>24.9</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>59</v>
+        <v>54.6</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.062</v>
+        <v>-0.132</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>27.8</v>
+        <v>26.6</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>35.3</v>
+        <v>33.25</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.0368</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>25.6</v>
+        <v>25.2</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.9</v>
+        <v>14.2</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.393</v>
+        <v>-0.3799</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>32</v>
+        <v>33.6</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1841</v>
+        <v>-0.1889</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>33.5</v>
+        <v>35.5</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>21.35</v>
+        <v>21.25</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>212.5</v>
+        <v>211.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.503</v>
+        <v>0.5385</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>29.4</v>
+        <v>31.1</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>48.2</v>
+        <v>49.4</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>80.6949</v>
+        <v>82.72879999999999</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>31.7</v>
+        <v>33.7</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.15</v>
+        <v>36</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0955</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>26.3</v>
+        <v>25.6</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>79.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5133</v>
+        <v>0.5019</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>31.2</v>
+        <v>29.8</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26</v>
+        <v>25.7</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1186</v>
+        <v>-0.1288</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>30.5</v>
+        <v>28</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>103.85</v>
+        <v>101.45</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4216</v>
+        <v>0.3888</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>26.8</v>
+        <v>25.8</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-28 01:15</t>
+          <t>2026-07-29 00:56</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>24.95</v>
+        <v>23.52</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.8359000000000001</v>
+        <v>0.7306999999999999</v>
       </c>
       <c r="H4" s="39" t="n">
         <v>25.4</v>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>38.97</v>
+        <v>37</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.7901</v>
+        <v>0.6995999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,22 +1017,22 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>44.55</v>
+        <v>42.2</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.0906</v>
+        <v>0.033</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>35.6</v>
+        <v>33.2</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J6" s="41" t="inlineStr">
-        <is>
-          <t>🟠 出清</t>
+      <c r="J6" s="42" t="inlineStr">
+        <is>
+          <t>🔴 停損</t>
         </is>
       </c>
     </row>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1755</v>
+        <v>1580</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3195</v>
+        <v>0.188</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>25.2</v>
+        <v>25.6</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2350</v>
+        <v>2280</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6151</v>
+        <v>0.5670000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
         <v>24.9</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>54.6</v>
+        <v>49.2</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.132</v>
+        <v>-0.2178</v>
       </c>
       <c r="H9" s="39" t="n">
         <v>26.6</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>33.25</v>
+        <v>30.85</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.1583</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>25.2</v>
+        <v>25.6</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3799</v>
+        <v>-0.3886</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>33.6</v>
+        <v>32.8</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>51.1</v>
+        <v>50.7</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1889</v>
+        <v>-0.1952</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>35.5</v>
+        <v>32.8</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>21.25</v>
+        <v>21.75</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>211.5</v>
+        <v>216.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>30.8</v>
+        <v>37.5</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>130</v>
+        <v>125.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.5385</v>
+        <v>0.4852</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>31.1</v>
+        <v>28.7</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>49.4</v>
+        <v>49.45</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>82.72879999999999</v>
+        <v>82.81360000000001</v>
       </c>
       <c r="H15" s="39" t="n">
         <v>33.7</v>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>36</v>
+        <v>35.4</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0955</v>
+        <v>-0.1106</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>25.6</v>
+        <v>30</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>79.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5019</v>
+        <v>0.4754</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>29.8</v>
+        <v>31.4</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>25.7</v>
+        <v>24.95</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1288</v>
+        <v>-0.1542</v>
       </c>
       <c r="H19" s="39" t="n">
         <v>28</v>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>101.45</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.3888</v>
+        <v>0.3299</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-29 00:56</t>
+          <t>2026-07-30 00:45</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>23.52</v>
+        <v>22.47</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.7306999999999999</v>
+        <v>0.6534</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>25.4</v>
+        <v>28.1</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>37</v>
+        <v>35.59</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.6995999999999999</v>
+        <v>0.6347999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>26.8</v>
+        <v>28.2</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>42.2</v>
+        <v>43.25</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.033</v>
+        <v>0.0588</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>33.2</v>
+        <v>39.8</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1580</v>
+        <v>1495</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.188</v>
+        <v>0.1241</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>25.6</v>
+        <v>27.7</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2280</v>
+        <v>2200</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.5670000000000001</v>
+        <v>0.512</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>24.9</v>
+        <v>28.2</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>49.2</v>
+        <v>45.5</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.2178</v>
+        <v>-0.2766</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>26.6</v>
+        <v>29.3</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>30.85</v>
+        <v>28.75</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1583</v>
+        <v>-0.2156</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>25.6</v>
+        <v>28.2</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14</v>
+        <v>13.85</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3886</v>
+        <v>-0.3952000000000001</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>32.8</v>
+        <v>33.5</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>50.7</v>
+        <v>50.1</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1952</v>
+        <v>-0.2048</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>32.8</v>
+        <v>34.7</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>21.75</v>
+        <v>21.7</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>216.5</v>
+        <v>216</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>37.5</v>
+        <v>35</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>125.5</v>
+        <v>123</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.4852</v>
+        <v>0.4556</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>28.7</v>
+        <v>31.4</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>49.45</v>
+        <v>49.9</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>82.81360000000001</v>
+        <v>83.57629999999999</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>33.7</v>
+        <v>37.3</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>-0.1106</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>30</v>
+        <v>32.8</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>77.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4754</v>
+        <v>0.4772999999999999</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>31.4</v>
+        <v>35.5</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>24.95</v>
+        <v>24.8</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1542</v>
+        <v>-0.1593</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>28</v>
+        <v>32.9</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>97.15000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.3299</v>
+        <v>0.2827</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>26</v>
+        <v>30.2</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-30 00:45</t>
+          <t>2026-07-31 00:57</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>22.47</v>
+        <v>24.49</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.6534</v>
+        <v>0.8020999999999999</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>28.1</v>
+        <v>29.5</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>35.59</v>
+        <v>39.03</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.6347999999999999</v>
+        <v>0.7928000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>43.25</v>
+        <v>43.2</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.0588</v>
+        <v>0.0575</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>39.8</v>
+        <v>35.8</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1495</v>
+        <v>1640</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.1241</v>
+        <v>0.2331</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>27.7</v>
+        <v>34.2</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2200</v>
+        <v>2425</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.512</v>
+        <v>0.6667000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>28.2</v>
+        <v>35.3</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>45.5</v>
+        <v>49.2</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.2766</v>
+        <v>-0.2178</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>29.3</v>
+        <v>31.1</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>28.75</v>
+        <v>31.15</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2156</v>
+        <v>-0.1501</v>
       </c>
       <c r="H10" s="39" t="n">
         <v>28.2</v>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.85</v>
+        <v>14.05</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3952000000000001</v>
+        <v>-0.3865</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>33.5</v>
+        <v>36.8</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>50.1</v>
+        <v>50.8</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.2048</v>
+        <v>-0.1937</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.4556</v>
+        <v>0.5385</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>31.4</v>
+        <v>36.2</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>49.9</v>
+        <v>53.1</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>83.57629999999999</v>
+        <v>89</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>37.3</v>
+        <v>35.5</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>35.4</v>
+        <v>35</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.1106</v>
+        <v>-0.1206</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>32.8</v>
+        <v>27.4</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>78</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4772999999999999</v>
+        <v>0.4697</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>35.5</v>
+        <v>33.4</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>24.8</v>
+        <v>24.75</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1593</v>
+        <v>-0.161</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>32.9</v>
+        <v>31.7</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>93.7</v>
+        <v>102.85</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.2827</v>
+        <v>0.4079</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>30.2</v>
+        <v>32.4</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-07-31 00:57</t>
+          <t>2026-08-04 01:23</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>24.49</v>
+        <v>24.6</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.8020999999999999</v>
+        <v>0.8101999999999999</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>29.5</v>
+        <v>27.5</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>39.03</v>
+        <v>38.95</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.7928000000000001</v>
+        <v>0.7892</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>28.3</v>
+        <v>30.3</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,22 +1017,22 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>43.2</v>
+        <v>44.45</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.0575</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>35.8</v>
+        <v>37.7</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J6" s="42" t="inlineStr">
-        <is>
-          <t>🔴 停損</t>
+      <c r="J6" s="41" t="inlineStr">
+        <is>
+          <t>🟠 出清</t>
         </is>
       </c>
     </row>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1640</v>
+        <v>1580</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.2331</v>
+        <v>0.188</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>34.2</v>
+        <v>29.5</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2425</v>
+        <v>2370</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.6289</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>35.3</v>
+        <v>29.7</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>49.2</v>
+        <v>49.85</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.2178</v>
+        <v>-0.2075</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>31.1</v>
+        <v>30</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>31.15</v>
+        <v>30.9</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1501</v>
+        <v>-0.1569</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>28.2</v>
+        <v>29.3</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.05</v>
+        <v>13.95</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3865</v>
+        <v>-0.3908</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>36.8</v>
+        <v>37</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>-0.1937</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>34.5</v>
+        <v>35.8</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>22.4</v>
+        <v>22.45</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>223</v>
+        <v>223.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>37</v>
+        <v>40.2</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>130</v>
+        <v>129.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.5385</v>
+        <v>0.5325</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>36.2</v>
+        <v>37.4</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>53.1</v>
+        <v>51.6</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>89</v>
+        <v>86.4576</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>35.5</v>
+        <v>34.4</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.1206</v>
+        <v>-0.108</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>27.4</v>
+        <v>29.4</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>0.4697</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>33.4</v>
+        <v>34.5</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>24.75</v>
+        <v>26.8</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.161</v>
+        <v>-0.0915</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>31.7</v>
+        <v>32.2</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>102.85</v>
+        <v>102</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4079</v>
+        <v>0.3963</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>32.4</v>
+        <v>30.3</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-08-04 01:23</t>
+          <t>2026-08-05 01:10</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>24.6</v>
+        <v>24.69</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.8101999999999999</v>
+        <v>0.8168000000000001</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>38.95</v>
+        <v>38.77</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.7892</v>
+        <v>0.7809</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>44.45</v>
+        <v>44.25</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.08810000000000001</v>
+        <v>0.0832</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>37.7</v>
+        <v>36.7</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1580</v>
+        <v>1620</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.188</v>
+        <v>0.218</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>29.5</v>
+        <v>31.5</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2370</v>
+        <v>2320</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6289</v>
+        <v>0.5945</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>29.7</v>
+        <v>28.4</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>49.85</v>
+        <v>51.4</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.2075</v>
+        <v>-0.1828</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>30</v>
+        <v>29.3</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>30.9</v>
+        <v>31.3</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1569</v>
+        <v>-0.146</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>29.3</v>
+        <v>29</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.95</v>
+        <v>13.9</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3908</v>
+        <v>-0.393</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>37</v>
+        <v>34.7</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1937</v>
+        <v>-0.1905</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>35.8</v>
+        <v>37.4</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>223.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>40.2</v>
+        <v>39.2</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>129.5</v>
+        <v>128.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.5325</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>37.4</v>
+        <v>36.4</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>51.6</v>
+        <v>50.7</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>86.4576</v>
+        <v>84.93219999999999</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>35.5</v>
+        <v>35.8</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.108</v>
+        <v>-0.1005</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>77.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4697</v>
+        <v>0.4678</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>34.5</v>
+        <v>32.5</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.8</v>
+        <v>26.25</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0915</v>
+        <v>-0.1102</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>32.2</v>
+        <v>30</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>102</v>
+        <v>100.65</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.3963</v>
+        <v>0.3778</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-08-05 01:10</t>
+          <t>2026-08-06 00:57</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>24.69</v>
+        <v>25.3</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.8168000000000001</v>
+        <v>0.8617</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>27.7</v>
+        <v>26.7</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>38.77</v>
+        <v>39.55</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.7809</v>
+        <v>0.8167</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>30</v>
+        <v>30.9</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>44.25</v>
+        <v>46.6</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.0832</v>
+        <v>0.1408</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>36.7</v>
+        <v>36.4</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1620</v>
+        <v>1650</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.218</v>
+        <v>0.2406</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>31.5</v>
+        <v>26.5</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2320</v>
+        <v>2370</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.5945</v>
+        <v>0.6289</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>51.4</v>
+        <v>53.7</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1828</v>
+        <v>-0.1463</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>29.3</v>
+        <v>28.3</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>31.3</v>
+        <v>31.35</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.146</v>
+        <v>-0.1446</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>29</v>
+        <v>26.2</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.9</v>
+        <v>14.05</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.393</v>
+        <v>-0.3865</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>34.7</v>
+        <v>36.7</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1905</v>
+        <v>-0.1984</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>37.4</v>
+        <v>33</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>22.45</v>
+        <v>22.5</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>223.5</v>
+        <v>224</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>39.2</v>
+        <v>38.2</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>128.5</v>
+        <v>127</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.503</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>36.4</v>
+        <v>32.4</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>84.93219999999999</v>
+        <v>85.27120000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>34.2</v>
+        <v>33.2</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>35.8</v>
+        <v>38.45</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.1005</v>
+        <v>-0.0339</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>29.2</v>
+        <v>33</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>77.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4678</v>
+        <v>0.4848</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.25</v>
+        <v>26.3</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1102</v>
+        <v>-0.1085</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>30</v>
+        <v>32.7</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>100.65</v>
+        <v>102.85</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.3778</v>
+        <v>0.4079</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-08-06 00:57</t>
+          <t>2026-08-11 00:13</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>25.3</v>
+        <v>25.82</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.8617</v>
+        <v>0.8998999999999999</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>26.7</v>
+        <v>28.7</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>39.55</v>
+        <v>40.18</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8167</v>
+        <v>0.8456999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>30.9</v>
+        <v>32.9</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>46.6</v>
+        <v>47.3</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1408</v>
+        <v>0.1579</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>36.4</v>
+        <v>36.9</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1650</v>
+        <v>1815</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.2406</v>
+        <v>0.3647</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>26.5</v>
+        <v>31.6</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2370</v>
+        <v>2380</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6289</v>
+        <v>0.6357</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>28.1</v>
+        <v>28.6</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>53.7</v>
+        <v>54</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1463</v>
+        <v>-0.1415</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>28.3</v>
+        <v>29</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>31.35</v>
+        <v>31.95</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1446</v>
+        <v>-0.1282</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>26.2</v>
+        <v>26.7</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.05</v>
+        <v>14.1</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3865</v>
+        <v>-0.3843</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>36.7</v>
+        <v>35.1</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>50.5</v>
+        <v>51.6</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1984</v>
+        <v>-0.181</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>33</v>
+        <v>39.2</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>22.5</v>
+        <v>20.45</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>224</v>
+        <v>203.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>38.2</v>
+        <v>34.5</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>127</v>
+        <v>128.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.503</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>32.4</v>
+        <v>34.4</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>85.27120000000001</v>
+        <v>85.44069999999999</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>33.2</v>
+        <v>31.8</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>38.45</v>
+        <v>37.95</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0339</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>78.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4848</v>
+        <v>0.483</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>32.4</v>
+        <v>32</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.3</v>
+        <v>26.8</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1085</v>
+        <v>-0.0915</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>32.7</v>
+        <v>33.6</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>102.85</v>
+        <v>104.25</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4079</v>
+        <v>0.4271</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>29</v>
+        <v>32.9</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-08-11 00:13</t>
+          <t>2026-08-12 00:15</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>25.82</v>
+        <v>25.93</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.8998999999999999</v>
+        <v>0.9079999999999999</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>28.7</v>
+        <v>31.5</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.18</v>
+        <v>40.38</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8456999999999999</v>
+        <v>0.8548</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>47.3</v>
+        <v>46.45</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1579</v>
+        <v>0.1371</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1815</v>
+        <v>1805</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3647</v>
+        <v>0.3571</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2380</v>
+        <v>2395</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6357</v>
+        <v>0.6459999999999999</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>28.6</v>
+        <v>33.7</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1415</v>
+        <v>-0.09380000000000001</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>29</v>
+        <v>32.1</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>31.95</v>
+        <v>31.75</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1282</v>
+        <v>-0.1337</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>26.7</v>
+        <v>28</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>-0.3843</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>35.1</v>
+        <v>36.7</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>51.6</v>
+        <v>52</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.181</v>
+        <v>-0.1746</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>39.2</v>
+        <v>40.2</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.45</v>
+        <v>20.25</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>203.5</v>
+        <v>201.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>34.5</v>
+        <v>33.9</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>128.5</v>
+        <v>128</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5147999999999999</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>51</v>
+        <v>49.4</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>85.44069999999999</v>
+        <v>82.72879999999999</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>31.8</v>
+        <v>30.5</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.95</v>
+        <v>38</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.04650000000000001</v>
+        <v>-0.0452</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>32.7</v>
+        <v>34</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>78.3</v>
+        <v>77.8</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.483</v>
+        <v>0.4735</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>32</v>
+        <v>34.5</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.8</v>
+        <v>26.65</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0915</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>33.6</v>
+        <v>36</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>104.25</v>
+        <v>104.6</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4271</v>
+        <v>0.4319</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-08-12 00:15</t>
+          <t>2026-08-13 00:15</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>25.93</v>
+        <v>26.08</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9079999999999999</v>
+        <v>0.9190999999999999</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.38</v>
+        <v>40.59</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8548</v>
+        <v>0.8645</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>34.5</v>
+        <v>35.6</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>46.45</v>
+        <v>46.85</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1371</v>
+        <v>0.1469</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1805</v>
+        <v>1790</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3571</v>
+        <v>0.3459</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2395</v>
+        <v>2415</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6459999999999999</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>33.7</v>
+        <v>31.2</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>57</v>
+        <v>55.4</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.09380000000000001</v>
+        <v>-0.1192</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>32.1</v>
+        <v>31.4</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>31.75</v>
+        <v>31.65</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1337</v>
+        <v>-0.1364</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.1</v>
+        <v>13.95</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3843</v>
+        <v>-0.3908</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>36.7</v>
+        <v>33.9</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>52</v>
+        <v>51.7</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1746</v>
+        <v>-0.1794</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>40.2</v>
+        <v>38.6</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.5147999999999999</v>
+        <v>0.503</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>34.5</v>
+        <v>33.8</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>49.4</v>
+        <v>48.7</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>82.72879999999999</v>
+        <v>81.5424</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>38</v>
+        <v>37.7</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0452</v>
+        <v>-0.0528</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>34</v>
+        <v>35.1</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>77.8</v>
+        <v>78.3</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4735</v>
+        <v>0.483</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>34.5</v>
+        <v>33.6</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.65</v>
+        <v>26.9</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.08810000000000001</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>104.6</v>
+        <v>105.2</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4319</v>
+        <v>0.4401</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-08-13 00:15</t>
+          <t>2026-08-14 00:14</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.08</v>
+        <v>26.5</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9190999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>31.6</v>
+        <v>32.2</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.59</v>
+        <v>41.24</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8645</v>
+        <v>0.8944</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>35.6</v>
+        <v>34.3</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>46.85</v>
+        <v>50</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1469</v>
+        <v>0.224</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>37.1</v>
+        <v>44.3</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1790</v>
+        <v>1885</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3459</v>
+        <v>0.4172999999999999</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2415</v>
+        <v>2400</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.6495000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>55.4</v>
+        <v>53.1</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1192</v>
+        <v>-0.1558</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>31.4</v>
+        <v>29.3</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>31.65</v>
+        <v>29.5</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1364</v>
+        <v>-0.1951</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>28.1</v>
+        <v>25.5</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>-0.3908</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>33.9</v>
+        <v>31.8</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>51.7</v>
+        <v>54.7</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1794</v>
+        <v>-0.1317</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>38.6</v>
+        <v>45.5</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>201.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>33.9</v>
+        <v>31.8</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>127</v>
+        <v>125.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.503</v>
+        <v>0.4852</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>33.8</v>
+        <v>30.6</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>48.7</v>
+        <v>46.6</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>81.5424</v>
+        <v>77.98310000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>30.4</v>
+        <v>28.5</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.7</v>
+        <v>37.95</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0528</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>35.1</v>
+        <v>29.7</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>78.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.483</v>
+        <v>0.5038</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>33.6</v>
+        <v>36.8</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.9</v>
+        <v>26.45</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.08810000000000001</v>
+        <v>-0.1034</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>36.1</v>
+        <v>27.5</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>105.2</v>
+        <v>106.45</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4401</v>
+        <v>0.4572</v>
       </c>
       <c r="H23" s="39" t="n">
         <v>33.5</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-08-14 00:14</t>
+          <t>2026-08-18 23:54</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.5</v>
+        <v>26.05</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.95</v>
+        <v>0.9168999999999999</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>32.2</v>
+        <v>30.6</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>41.24</v>
+        <v>40.58</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8944</v>
+        <v>0.8640000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>34.3</v>
+        <v>31.5</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.224</v>
+        <v>0.2166</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>44.3</v>
+        <v>37.5</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1885</v>
+        <v>1820</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.4172999999999999</v>
+        <v>0.3684000000000001</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>32.2</v>
+        <v>31.4</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2400</v>
+        <v>2380</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6495000000000001</v>
+        <v>0.6357</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>31.4</v>
+        <v>30.1</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>53.1</v>
+        <v>51.3</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1558</v>
+        <v>-0.1844</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>29.3</v>
+        <v>27.7</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>29.5</v>
+        <v>28.75</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1951</v>
+        <v>-0.2156</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>25.5</v>
+        <v>26.2</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.95</v>
+        <v>13.9</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3908</v>
+        <v>-0.393</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>31.8</v>
+        <v>32.5</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>54.7</v>
+        <v>56.2</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1317</v>
+        <v>-0.1079</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.25</v>
+        <v>20.1</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>201.5</v>
+        <v>200</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>31.8</v>
+        <v>32.5</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>125.5</v>
+        <v>129.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.4852</v>
+        <v>0.5325</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>30.6</v>
+        <v>35.4</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>46.6</v>
+        <v>46.9</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>77.98310000000001</v>
+        <v>78.4915</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>28.5</v>
+        <v>29.9</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.95</v>
+        <v>37.9</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.04650000000000001</v>
+        <v>-0.04769999999999999</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>29.7</v>
+        <v>30.7</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>79.40000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5038</v>
+        <v>0.4924</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>36.8</v>
+        <v>31.9</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.45</v>
+        <v>27.1</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1034</v>
+        <v>-0.0814</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>27.5</v>
+        <v>35.1</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>106.45</v>
+        <v>104.9</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4572</v>
+        <v>0.436</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>33.5</v>
+        <v>29.4</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-08-18 23:54</t>
+          <t>2026-08-19 23:54</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.05</v>
+        <v>25.59</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9168999999999999</v>
+        <v>0.883</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.58</v>
+        <v>39.93</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8640000000000001</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.2166</v>
+        <v>0.224</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>37.5</v>
+        <v>38.7</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1820</v>
+        <v>1765</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3684000000000001</v>
+        <v>0.3271</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>31.4</v>
+        <v>30.4</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2380</v>
+        <v>2350</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6357</v>
+        <v>0.6151</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>30.1</v>
+        <v>28.6</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1844</v>
+        <v>-0.1924</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>27.7</v>
+        <v>28.2</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>28.75</v>
+        <v>28.55</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2156</v>
+        <v>-0.221</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>26.2</v>
+        <v>26.7</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.393</v>
+        <v>-0.3886</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>32.5</v>
+        <v>35.7</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,22 +1269,22 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>56.2</v>
+        <v>59</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1079</v>
+        <v>-0.0635</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>45.4</v>
+        <v>45.9</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J12" s="42" t="inlineStr">
-        <is>
-          <t>🔴 停損</t>
+      <c r="J12" s="45" t="inlineStr">
+        <is>
+          <t>⚪ 觀察</t>
         </is>
       </c>
     </row>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>129.5</v>
+        <v>128.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.5325</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>35.4</v>
+        <v>34.4</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>46.9</v>
+        <v>47.05</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>78.4915</v>
+        <v>78.7458</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>29.9</v>
+        <v>29.4</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.9</v>
+        <v>37.75</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.04769999999999999</v>
+        <v>-0.0515</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>30.7</v>
+        <v>31.2</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>78.8</v>
+        <v>79.2</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4924</v>
+        <v>0.5</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>31.9</v>
+        <v>34.4</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>27.1</v>
+        <v>26.7</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0814</v>
+        <v>-0.0949</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>35.1</v>
+        <v>28.7</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>104.9</v>
+        <v>103.1</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.436</v>
+        <v>0.4114</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>29.4</v>
+        <v>31.4</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-08-19 23:54</t>
+          <t>2026-08-20 23:55</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>25.59</v>
+        <v>25.75</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.883</v>
+        <v>0.8948</v>
       </c>
       <c r="H4" s="39" t="n">
         <v>30.4</v>
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>39.93</v>
+        <v>40.05</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.8397</v>
       </c>
       <c r="H5" s="39" t="n">
         <v>31.4</v>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.224</v>
+        <v>0.2362</v>
       </c>
       <c r="H6" s="39" t="n">
         <v>38.7</v>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1765</v>
+        <v>1745</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3271</v>
+        <v>0.312</v>
       </c>
       <c r="H7" s="39" t="n">
         <v>30.4</v>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2350</v>
+        <v>2375</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6151</v>
+        <v>0.6323</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>28.6</v>
+        <v>30.6</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1924</v>
+        <v>-0.1892</v>
       </c>
       <c r="H9" s="39" t="n">
         <v>28.2</v>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>28.55</v>
+        <v>28.6</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.221</v>
+        <v>-0.2196</v>
       </c>
       <c r="H10" s="39" t="n">
         <v>26.7</v>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14</v>
+        <v>14.05</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3886</v>
+        <v>-0.3865</v>
       </c>
       <c r="H11" s="39" t="n">
         <v>35.7</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>59</v>
+        <v>60.3</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.0635</v>
+        <v>-0.0429</v>
       </c>
       <c r="H12" s="39" t="n">
         <v>45.9</v>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H13" s="39" t="n">
         <v>33</v>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>128.5</v>
+        <v>128</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5147999999999999</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>34.4</v>
+        <v>32.9</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>47.05</v>
+        <v>46.4</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>78.7458</v>
+        <v>77.64409999999999</v>
       </c>
       <c r="H15" s="39" t="n">
         <v>29.4</v>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.75</v>
+        <v>38.65</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0515</v>
+        <v>-0.0289</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>31.2</v>
+        <v>35.7</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>79.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5</v>
+        <v>0.5322</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>34.4</v>
+        <v>44.7</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.7</v>
+        <v>27.1</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0949</v>
+        <v>-0.0814</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>28.7</v>
+        <v>33.2</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>103.1</v>
+        <v>103.8</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4114</v>
+        <v>0.4209000000000001</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>31.4</v>
+        <v>30.4</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-08-20 23:55</t>
+          <t>2026-08-21 23:55</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>25.75</v>
+        <v>25.81</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.8948</v>
+        <v>0.8992</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>30.4</v>
+        <v>29.4</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.05</v>
+        <v>40.26</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8397</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>31.4</v>
+        <v>29.9</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.2362</v>
+        <v>0.2313</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>38.7</v>
+        <v>36.7</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1745</v>
+        <v>1750</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.312</v>
+        <v>0.3158</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>30.4</v>
+        <v>29.9</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2375</v>
+        <v>2410</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6323</v>
+        <v>0.6564</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>30.6</v>
+        <v>33.1</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1892</v>
+        <v>-0.194</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>28.2</v>
+        <v>27.7</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>28.6</v>
+        <v>28.45</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2196</v>
+        <v>-0.2237</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>26.7</v>
+        <v>26.2</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.05</v>
+        <v>14.35</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3865</v>
+        <v>-0.3734</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>35.7</v>
+        <v>42.3</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="G12" s="43" t="n">
-        <v>-0.0429</v>
+        <v>64</v>
+      </c>
+      <c r="G12" s="38" t="n">
+        <v>0.0159</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>45.9</v>
+        <v>45.4</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20</v>
+        <v>20.4</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.5147999999999999</v>
+        <v>0.5858</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>32.9</v>
+        <v>41.7</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>46.4</v>
+        <v>46.95</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>77.64409999999999</v>
+        <v>78.5763</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>29.4</v>
+        <v>30.9</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>38.65</v>
+        <v>38.5</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0289</v>
+        <v>-0.0327</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>35.7</v>
+        <v>32.2</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>80.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5322</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>44.7</v>
+        <v>40.9</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>27.1</v>
+        <v>26.85</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0814</v>
+        <v>-0.0898</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>33.2</v>
+        <v>31.2</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>103.8</v>
+        <v>104.65</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4209000000000001</v>
+        <v>0.4326</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>30.4</v>
+        <v>31.4</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-08-21 23:55</t>
+          <t>2026-08-25 00:01</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>25.81</v>
+        <v>25.76</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.8992</v>
+        <v>0.8955</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>29.4</v>
+        <v>30.2</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.26</v>
+        <v>40.04</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.8392000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>29.9</v>
+        <v>32.5</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>50.3</v>
+        <v>51</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.2313</v>
+        <v>0.2485</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>36.7</v>
+        <v>37</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1750</v>
+        <v>1735</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3158</v>
+        <v>0.3045</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>29.9</v>
+        <v>30.2</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2410</v>
+        <v>2375</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6564</v>
+        <v>0.6323</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>33.1</v>
+        <v>30.7</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.194</v>
+        <v>-0.1955</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>27.7</v>
+        <v>28.8</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>28.45</v>
+        <v>28.3</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2237</v>
+        <v>-0.2278</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>26.2</v>
+        <v>26.5</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.35</v>
+        <v>14.45</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3734</v>
+        <v>-0.369</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>42.3</v>
+        <v>40.8</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,22 +1269,22 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>64</v>
+        <v>64.5</v>
       </c>
       <c r="G12" s="38" t="n">
-        <v>0.0159</v>
+        <v>0.0238</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>45.4</v>
+        <v>39.7</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J12" s="45" t="inlineStr">
-        <is>
-          <t>⚪ 觀察</t>
+      <c r="J12" s="42" t="inlineStr">
+        <is>
+          <t>🔴 停損</t>
         </is>
       </c>
     </row>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.5858</v>
+        <v>0.5621</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>41.7</v>
+        <v>35</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>46.95</v>
+        <v>46.85</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>78.5763</v>
+        <v>78.4068</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>30.9</v>
+        <v>31.2</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0327</v>
+        <v>-0.0352</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>32.2</v>
+        <v>31</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>80.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5189</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>40.9</v>
+        <v>42</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.85</v>
+        <v>27.2</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0898</v>
+        <v>-0.078</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>31.2</v>
+        <v>33</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>104.65</v>
+        <v>103.8</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4326</v>
+        <v>0.4209000000000001</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>31.4</v>
+        <v>32.5</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-08-25 00:01</t>
+          <t>2026-08-26 00:05</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>25.76</v>
+        <v>25.73</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.8955</v>
+        <v>0.8933</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>30.2</v>
+        <v>32</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.04</v>
+        <v>40.37</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8392000000000001</v>
+        <v>0.8543999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>32.5</v>
+        <v>32.8</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.2485</v>
+        <v>0.2387</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>37</v>
+        <v>36.3</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1735</v>
+        <v>1710</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3045</v>
+        <v>0.2857</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>30.2</v>
+        <v>27.5</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2375</v>
+        <v>2400</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6323</v>
+        <v>0.6495000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>30.7</v>
+        <v>32.7</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1955</v>
+        <v>-0.1987</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>28.8</v>
+        <v>29.1</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>-0.2278</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>26.5</v>
+        <v>28.8</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.45</v>
+        <v>14.3</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.369</v>
+        <v>-0.3754999999999999</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>40.8</v>
+        <v>38.6</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>64.5</v>
+        <v>63.6</v>
       </c>
       <c r="G12" s="38" t="n">
-        <v>0.0238</v>
+        <v>0.0095</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>39.7</v>
+        <v>38.3</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>132</v>
+        <v>141.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.5621</v>
+        <v>0.6746</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>35</v>
+        <v>40.2</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>46.85</v>
+        <v>47</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>78.4068</v>
+        <v>78.661</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>31.2</v>
+        <v>29.4</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>38.4</v>
+        <v>37.95</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0352</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>31</v>
+        <v>28.8</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>80.2</v>
+        <v>75.3</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.5189</v>
+        <v>0.4261</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>42</v>
+        <v>34.1</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>-0.078</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>33</v>
+        <v>30.8</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>103.8</v>
+        <v>104.4</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4209000000000001</v>
+        <v>0.4292</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>32.5</v>
+        <v>33.3</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-08-26 00:05</t>
+          <t>2026-08-27 00:35</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>25.73</v>
+        <v>26.35</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.8933</v>
+        <v>0.9389</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>32</v>
+        <v>35.3</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.37</v>
+        <v>41.06</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8543999999999999</v>
+        <v>0.8861</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>32.8</v>
+        <v>39.8</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>50.6</v>
+        <v>48.65</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.2387</v>
+        <v>0.1909</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>36.3</v>
+        <v>37.4</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1710</v>
+        <v>1770</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.2857</v>
+        <v>0.3308</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>27.5</v>
+        <v>33.6</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2400</v>
+        <v>2410</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6495000000000001</v>
+        <v>0.6564</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>32.7</v>
+        <v>34.5</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1987</v>
+        <v>-0.194</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>29.1</v>
+        <v>30.9</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>28.3</v>
+        <v>28.7</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2278</v>
+        <v>-0.2169</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>28.8</v>
+        <v>29.6</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.3</v>
+        <v>14.25</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3754999999999999</v>
+        <v>-0.3777</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>38.6</v>
+        <v>37.4</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="G12" s="38" t="n">
-        <v>0.0095</v>
+        <v>57.9</v>
+      </c>
+      <c r="G12" s="43" t="n">
+        <v>-0.081</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>38.3</v>
+        <v>35.3</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.4</v>
+        <v>20.8</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>32.6</v>
+        <v>33.9</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>0.6746</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>40.2</v>
+        <v>34.6</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>47</v>
+        <v>46.15</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>78.661</v>
+        <v>77.22029999999999</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>29.4</v>
+        <v>31.8</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.95</v>
+        <v>37.6</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.04650000000000001</v>
+        <v>-0.0553</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>28.8</v>
+        <v>30.6</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>75.3</v>
+        <v>75.7</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4261</v>
+        <v>0.4337</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>34.1</v>
+        <v>32.9</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.078</v>
+        <v>-0.08470000000000001</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>30.8</v>
+        <v>31.1</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>104.4</v>
+        <v>106.05</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4292</v>
+        <v>0.4517</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>33.3</v>
+        <v>38.7</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-08-27 00:35</t>
+          <t>2026-08-28 08:28</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.35</v>
+        <v>26.57</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9389</v>
+        <v>0.9551000000000001</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>35.3</v>
+        <v>34.7</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>41.06</v>
+        <v>41.53</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8861</v>
+        <v>0.9077</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>39.8</v>
+        <v>37.6</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>48.65</v>
+        <v>48.4</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1909</v>
+        <v>0.1848</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>37.4</v>
+        <v>36.8</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1770</v>
+        <v>1830</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3308</v>
+        <v>0.3759</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2410</v>
+        <v>2420</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6564</v>
+        <v>0.6631999999999999</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>34.5</v>
+        <v>32.9</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>50.7</v>
+        <v>51.8</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.194</v>
+        <v>-0.1765</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>30.9</v>
+        <v>33</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>28.7</v>
+        <v>28.65</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2169</v>
+        <v>-0.2183</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>29.6</v>
+        <v>27.9</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.25</v>
+        <v>14.15</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3777</v>
+        <v>-0.3821</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>37.4</v>
+        <v>34.5</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>57.9</v>
+        <v>56.2</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.081</v>
+        <v>-0.1079</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>35.3</v>
+        <v>34.7</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.8</v>
+        <v>20.35</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>207</v>
+        <v>202.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>141.5</v>
+        <v>144</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.6746</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>34.6</v>
+        <v>35.4</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>46.15</v>
+        <v>48.2</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>77.22029999999999</v>
+        <v>80.6949</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>31.8</v>
+        <v>34.6</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0553</v>
+        <v>-0.0603</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>30.6</v>
+        <v>30</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>75.7</v>
+        <v>75.3</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4337</v>
+        <v>0.4261</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>32.9</v>
+        <v>32.3</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.08470000000000001</v>
+        <v>-0.0814</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>31.1</v>
+        <v>32</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>106.05</v>
+        <v>106.95</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4517</v>
+        <v>0.4641</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>38.7</v>
+        <v>36.5</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-08-28 08:28</t>
+          <t>2026-09-01 04:54</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.57</v>
+        <v>26.21</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9551000000000001</v>
+        <v>0.9286</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>34.7</v>
+        <v>32.3</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>41.53</v>
+        <v>41.22</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9077</v>
+        <v>0.8934000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>37.6</v>
+        <v>35.3</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>48.4</v>
+        <v>48.8</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1848</v>
+        <v>0.1946</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>36.8</v>
+        <v>32.8</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1830</v>
+        <v>1840</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3759</v>
+        <v>0.3835</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>33.7</v>
+        <v>31.3</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6631999999999999</v>
+        <v>0.6529</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>32.9</v>
+        <v>29.4</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>51.8</v>
+        <v>51.1</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1765</v>
+        <v>-0.1876</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>33</v>
+        <v>28.6</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>28.65</v>
+        <v>28.05</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2183</v>
+        <v>-0.2347</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>27.9</v>
+        <v>25.3</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.15</v>
+        <v>14</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3821</v>
+        <v>-0.3886</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>34.5</v>
+        <v>31.6</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>56.2</v>
+        <v>59.5</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.1079</v>
+        <v>-0.0556</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>34.7</v>
+        <v>40.5</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.35</v>
+        <v>20.25</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>202.5</v>
+        <v>201.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>33.8</v>
+        <v>31.6</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>0.7040999999999999</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>48.2</v>
+        <v>48.55</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>80.6949</v>
+        <v>81.2881</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>34.6</v>
+        <v>28.1</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.4</v>
+        <v>37.35</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0603</v>
+        <v>-0.0616</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>30</v>
+        <v>28.3</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>75.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4261</v>
+        <v>0.428</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>32.3</v>
+        <v>30.6</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0814</v>
+        <v>-0.0915</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>32</v>
+        <v>27.7</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>106.95</v>
+        <v>106.25</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4641</v>
+        <v>0.4545</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>36.5</v>
+        <v>34.6</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-01 04:54</t>
+          <t>2026-09-02 02:40</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.21</v>
+        <v>26.78</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9286</v>
+        <v>0.9706</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>32.3</v>
+        <v>35.4</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>41.22</v>
+        <v>42.4</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8934000000000001</v>
+        <v>0.9476</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>35.3</v>
+        <v>44.2</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>48.8</v>
+        <v>49.8</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1946</v>
+        <v>0.2191</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>32.8</v>
+        <v>36.2</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1840</v>
+        <v>1865</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3835</v>
+        <v>0.4023</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>31.3</v>
+        <v>33.8</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2405</v>
+        <v>2440</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6529</v>
+        <v>0.677</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>29.4</v>
+        <v>33.3</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1876</v>
+        <v>-0.1812</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>28.6</v>
+        <v>31.7</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>28.05</v>
+        <v>28.4</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2347</v>
+        <v>-0.2251</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>25.3</v>
+        <v>28.4</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3886</v>
+        <v>-0.3843</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>31.6</v>
+        <v>34.7</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>59.5</v>
+        <v>57.6</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.0556</v>
+        <v>-0.0857</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>40.5</v>
+        <v>35.1</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.25</v>
+        <v>20.35</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>201.5</v>
+        <v>202.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>31.6</v>
+        <v>33.2</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.716</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>48.55</v>
+        <v>48.5</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>81.2881</v>
+        <v>81.2034</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>28.1</v>
+        <v>29.6</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>37.35</v>
+        <v>36.25</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0616</v>
+        <v>-0.0892</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>28.3</v>
+        <v>27.5</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>75.40000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.428</v>
+        <v>0.4375</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>30.6</v>
+        <v>31.7</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.8</v>
+        <v>26.75</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0915</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>27.7</v>
+        <v>29.9</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>106.25</v>
+        <v>108.45</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4545</v>
+        <v>0.4846</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>34.6</v>
+        <v>38.4</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-02 02:40</t>
+          <t>2026-09-03 02:49</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -939,7 +939,7 @@
         <v>0.9706</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>35.4</v>
+        <v>36</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>0.9476</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>44.2</v>
+        <v>44.9</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>0.2191</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>36.2</v>
+        <v>36.8</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>0.4023</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>33.8</v>
+        <v>34.5</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>0.677</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>33.3</v>
+        <v>34.2</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>-0.1812</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>31.7</v>
+        <v>32.3</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>-0.2251</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>28.4</v>
+        <v>29</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>-0.3843</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>34.7</v>
+        <v>35.3</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>-0.0857</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>35.1</v>
+        <v>35.7</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>202.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>33.2</v>
+        <v>33.8</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>0.716</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>35.6</v>
+        <v>36.2</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>81.2034</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>29.6</v>
+        <v>30.2</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>-0.0892</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>27.5</v>
+        <v>28.1</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>0.4375</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>31.7</v>
+        <v>32.3</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>-0.09320000000000001</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>29.9</v>
+        <v>30.5</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>0.4846</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>38.4</v>
+        <v>39.1</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-03 02:49</t>
+          <t>2026-09-04 02:48</t>
         </is>
       </c>
     </row>
